--- a/Market data utilities.xlsx
+++ b/Market data utilities.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Macro\Python\Utilities CHF streamlit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Macro\Python\Streamlit présentation Satom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E93811A-D953-40B9-9138-8640D89F1620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C786263-45FE-4B2F-9BE6-AB4C503C81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="490">
   <si>
     <t>ID</t>
   </si>
@@ -621,25 +621,10 @@
     <t>DG5714416 Corp @SWEX Corp</t>
   </si>
   <si>
-    <t>ZS640902 Corp</t>
-  </si>
-  <si>
-    <t>ZS640902 Corp @SWEX Corp</t>
-  </si>
-  <si>
     <t>GRANDE DIXENCE</t>
   </si>
   <si>
     <t>GRANDX</t>
-  </si>
-  <si>
-    <t>14.05.2019</t>
-  </si>
-  <si>
-    <t>17.06.2019</t>
-  </si>
-  <si>
-    <t>17.06.2026</t>
   </si>
   <si>
     <t>CH,RAIFFS</t>
@@ -1839,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF81"/>
+  <dimension ref="A1:AF80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1987,7 +1972,7 @@
         <v>100.68300000000001</v>
       </c>
       <c r="O2">
-        <v>3.375</v>
+        <v>3.3583333333333334</v>
       </c>
       <c r="P2">
         <v>5.5456046791990572E-3</v>
@@ -1999,40 +1984,40 @@
         <v>-2.4499999999999999E-3</v>
       </c>
       <c r="S2">
-        <v>53.230767461750261</v>
+        <v>56.959536400174393</v>
       </c>
       <c r="T2">
-        <v>47.183675043050691</v>
+        <v>46.286547183601598</v>
       </c>
       <c r="U2">
-        <v>50.205244007558726</v>
+        <v>51.61691096555483</v>
       </c>
       <c r="V2">
-        <v>0.2134375</v>
+        <v>0.28362500000000002</v>
       </c>
       <c r="W2">
-        <v>0.2734375</v>
+        <v>0.34362500000000001</v>
       </c>
       <c r="X2">
-        <v>0.2434375</v>
+        <v>0.31362499999999999</v>
       </c>
       <c r="Y2">
+        <v>99.15</v>
+      </c>
+      <c r="Z2">
         <v>99.5</v>
       </c>
-      <c r="Z2">
-        <v>99.7</v>
-      </c>
       <c r="AA2">
-        <v>99.6</v>
+        <v>99.325000000000003</v>
       </c>
       <c r="AB2">
-        <v>0.77574517461750259</v>
+        <v>0.88322036400174397</v>
       </c>
       <c r="AC2">
-        <v>0.71527425043050685</v>
+        <v>0.77649047183601594</v>
       </c>
       <c r="AD2">
-        <v>0.74548994007558722</v>
+        <v>0.82979410965554823</v>
       </c>
       <c r="AE2" t="s">
         <v>40</v>
@@ -2085,7 +2070,7 @@
         <v>100.696</v>
       </c>
       <c r="O3">
-        <v>3.2805555555555554</v>
+        <v>3.2638888888888888</v>
       </c>
       <c r="P3">
         <v>1.3949466762315125E-2</v>
@@ -2097,40 +2082,40 @@
         <v>1.2075000000000001E-2</v>
       </c>
       <c r="S3">
-        <v>44.122171126368478</v>
+        <v>42.656360171654121</v>
       </c>
       <c r="T3">
-        <v>35.009173016586608</v>
+        <v>35.002371512014022</v>
       </c>
       <c r="U3">
-        <v>39.561288322013404</v>
+        <v>38.826287307349197</v>
       </c>
       <c r="V3">
-        <v>0.20753472222222222</v>
+        <v>0.27937499999999998</v>
       </c>
       <c r="W3">
-        <v>0.26753472222222219</v>
+        <v>0.33937499999999998</v>
       </c>
       <c r="X3">
-        <v>0.23753472222222222</v>
+        <v>0.30937500000000001</v>
       </c>
       <c r="Y3">
-        <v>102.65</v>
+        <v>102.45</v>
       </c>
       <c r="Z3">
-        <v>102.95</v>
+        <v>102.7</v>
       </c>
       <c r="AA3">
-        <v>102.80000000000001</v>
+        <v>102.575</v>
       </c>
       <c r="AB3">
-        <v>0.67875643348590697</v>
+        <v>0.73593860171654124</v>
       </c>
       <c r="AC3">
-        <v>0.58762645238808831</v>
+        <v>0.65939871512014026</v>
       </c>
       <c r="AD3">
-        <v>0.63314760544235626</v>
+        <v>0.69763787307349201</v>
       </c>
       <c r="AE3" t="s">
         <v>40</v>
@@ -2183,7 +2168,7 @@
         <v>100.232</v>
       </c>
       <c r="O4">
-        <v>1.3472222222222223</v>
+        <v>1.3305555555555555</v>
       </c>
       <c r="P4">
         <v>1.4149549643148759E-2</v>
@@ -2195,40 +2180,40 @@
         <v>-5.3500000000000006E-3</v>
       </c>
       <c r="S4">
-        <v>97.422142728452059</v>
+        <v>99.423843301095985</v>
       </c>
       <c r="T4">
-        <v>82.438320194333272</v>
+        <v>84.219513878379331</v>
       </c>
       <c r="U4">
-        <v>89.923734735615184</v>
+        <v>91.815042669635886</v>
       </c>
       <c r="V4">
-        <v>6.711805555555557E-2</v>
+        <v>0.14131944444444444</v>
       </c>
       <c r="W4">
-        <v>0.12711805555555555</v>
+        <v>0.20131944444444444</v>
       </c>
       <c r="X4">
-        <v>9.7118055555555569E-2</v>
+        <v>0.17131944444444444</v>
       </c>
       <c r="Y4">
-        <v>100.5</v>
+        <v>100.37</v>
       </c>
       <c r="Z4">
-        <v>100.7</v>
+        <v>100.57</v>
       </c>
       <c r="AA4">
-        <v>100.6</v>
+        <v>100.47</v>
       </c>
       <c r="AB4">
-        <v>1.0713394828400762</v>
+        <v>1.1655578774554043</v>
       </c>
       <c r="AC4">
-        <v>0.92150125749888823</v>
+        <v>1.0135145832282377</v>
       </c>
       <c r="AD4">
-        <v>0.99635540291170732</v>
+        <v>1.0894698711408033</v>
       </c>
       <c r="AE4" t="s">
         <v>40</v>
@@ -2281,7 +2266,7 @@
         <v>100.16800000000001</v>
       </c>
       <c r="O5">
-        <v>7.6</v>
+        <v>7.583333333333333</v>
       </c>
       <c r="P5">
         <v>1.5774820651296064E-2</v>
@@ -2293,40 +2278,40 @@
         <v>3.2500000000000003E-3</v>
       </c>
       <c r="S5">
-        <v>96.073295532794873</v>
+        <v>100.64282024461608</v>
       </c>
       <c r="T5">
-        <v>94.685183196727223</v>
+        <v>90.872068941383347</v>
       </c>
       <c r="U5">
-        <v>95.379038852909559</v>
+        <v>95.747533287382893</v>
       </c>
       <c r="V5">
-        <v>0.441</v>
+        <v>0.47875000000000001</v>
       </c>
       <c r="W5">
-        <v>0.501</v>
+        <v>0.53874999999999995</v>
       </c>
       <c r="X5">
-        <v>0.47099999999999997</v>
+        <v>0.50874999999999992</v>
       </c>
       <c r="Y5">
-        <v>101.2</v>
+        <v>100.6</v>
       </c>
       <c r="Z5">
         <v>101.3</v>
       </c>
       <c r="AA5">
-        <v>101.25</v>
+        <v>100.94999999999999</v>
       </c>
       <c r="AB5">
-        <v>1.4317329553279488</v>
+        <v>1.5151782024461606</v>
       </c>
       <c r="AC5">
-        <v>1.4178518319672722</v>
+        <v>1.4174706894138334</v>
       </c>
       <c r="AD5">
-        <v>1.4247903885290956</v>
+        <v>1.4662253328738288</v>
       </c>
       <c r="AE5" t="s">
         <v>40</v>
@@ -2379,7 +2364,7 @@
         <v>100.08800000000001</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.5833333333333335</v>
       </c>
       <c r="P6">
         <v>1.0274320242513223E-2</v>
@@ -2391,40 +2376,40 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="S6">
-        <v>77.788606288104205</v>
+        <v>89.822002097736785</v>
       </c>
       <c r="T6">
-        <v>76.365774007531485</v>
+        <v>76.883017930332031</v>
       </c>
       <c r="U6">
-        <v>77.077075616436417</v>
+        <v>83.343084857452737</v>
       </c>
       <c r="V6">
-        <v>0.22750000000000001</v>
+        <v>0.29375000000000001</v>
       </c>
       <c r="W6">
-        <v>0.28749999999999998</v>
+        <v>0.35375000000000001</v>
       </c>
       <c r="X6">
-        <v>0.25750000000000001</v>
+        <v>0.32375000000000004</v>
       </c>
       <c r="Y6">
-        <v>100.05</v>
+        <v>99.4</v>
       </c>
       <c r="Z6">
-        <v>100.1</v>
+        <v>99.85</v>
       </c>
       <c r="AA6">
-        <v>100.07499999999999</v>
+        <v>99.625</v>
       </c>
       <c r="AB6">
-        <v>1.0353860628810421</v>
+        <v>1.2219700209773678</v>
       </c>
       <c r="AC6">
-        <v>1.0211577400753149</v>
+        <v>1.0925801793033203</v>
       </c>
       <c r="AD6">
-        <v>1.0282707561643643</v>
+        <v>1.1571808485745274</v>
       </c>
       <c r="AE6" t="s">
         <v>40</v>
@@ -2477,7 +2462,7 @@
         <v>100.324</v>
       </c>
       <c r="O7">
-        <v>0.26666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="P7">
         <v>1.669724894429378E-2</v>
@@ -2489,40 +2474,40 @@
         <v>1.7749999999999999E-3</v>
       </c>
       <c r="S7">
-        <v>44.168064212816702</v>
+        <v>42.878387990806885</v>
       </c>
       <c r="T7">
-        <v>25.275091342360778</v>
+        <v>26.73345711780216</v>
       </c>
       <c r="U7">
-        <v>34.715968282585045</v>
+        <v>34.801880527441895</v>
       </c>
       <c r="V7">
-        <v>-6.8126666666666669E-2</v>
+        <v>-6.4699999999999994E-2</v>
       </c>
       <c r="W7">
-        <v>-8.126666666666664E-3</v>
+        <v>-4.6999999999999993E-3</v>
       </c>
       <c r="X7">
-        <v>-3.8126666666666663E-2</v>
+        <v>-3.4699999999999995E-2</v>
       </c>
       <c r="Y7">
+        <v>100.33</v>
+      </c>
+      <c r="Z7">
+        <v>100.37</v>
+      </c>
+      <c r="AA7">
         <v>100.35</v>
       </c>
-      <c r="Z7">
-        <v>100.4</v>
-      </c>
-      <c r="AA7">
-        <v>100.375</v>
-      </c>
       <c r="AB7">
-        <v>0.40355397546150035</v>
+        <v>0.39408387990806887</v>
       </c>
       <c r="AC7">
-        <v>0.21462424675694114</v>
+        <v>0.23263457117802161</v>
       </c>
       <c r="AD7">
-        <v>0.30903301615918383</v>
+        <v>0.31331880527441897</v>
       </c>
       <c r="AE7" t="s">
         <v>40</v>
@@ -2575,7 +2560,7 @@
         <v>100.434</v>
       </c>
       <c r="O8">
-        <v>1.1138888888888889</v>
+        <v>1.0972222222222223</v>
       </c>
       <c r="P8">
         <v>3.0095225595174076E-2</v>
@@ -2587,40 +2572,40 @@
         <v>1.805E-2</v>
       </c>
       <c r="S8">
-        <v>54.217751390968161</v>
+        <v>51.933199029831215</v>
       </c>
       <c r="T8">
-        <v>40.099207932300338</v>
+        <v>41.165574918658599</v>
       </c>
       <c r="U8">
-        <v>47.153262342806499</v>
+        <v>46.54637756825214</v>
       </c>
       <c r="V8">
-        <v>4.5534722222222226E-2</v>
+        <v>0.1121527777777778</v>
       </c>
       <c r="W8">
-        <v>0.10553472222222222</v>
+        <v>0.17215277777777779</v>
       </c>
       <c r="X8">
-        <v>7.5534722222222225E-2</v>
+        <v>0.14215277777777779</v>
       </c>
       <c r="Y8">
-        <v>102.76</v>
+        <v>102.67</v>
       </c>
       <c r="Z8">
-        <v>102.92</v>
+        <v>102.79</v>
       </c>
       <c r="AA8">
-        <v>102.84</v>
+        <v>102.73</v>
       </c>
       <c r="AB8">
-        <v>0.61771223613190385</v>
+        <v>0.66148476807608991</v>
       </c>
       <c r="AC8">
-        <v>0.47652680154522564</v>
+        <v>0.55380852696436378</v>
       </c>
       <c r="AD8">
-        <v>0.54706734565028725</v>
+        <v>0.60761655346029919</v>
       </c>
       <c r="AE8" t="s">
         <v>40</v>
@@ -2673,7 +2658,7 @@
         <v>100.26300000000001</v>
       </c>
       <c r="O9">
-        <v>4.1138888888888889</v>
+        <v>4.0972222222222223</v>
       </c>
       <c r="P9">
         <v>3.3320218026128001E-2</v>
@@ -2685,40 +2670,40 @@
         <v>1.8775E-2</v>
       </c>
       <c r="S9">
-        <v>72.542413673453183</v>
+        <v>70.588828338954741</v>
       </c>
       <c r="T9">
-        <v>65.485004161334757</v>
+        <v>65.852234347145156</v>
       </c>
       <c r="U9">
-        <v>69.01061206002808</v>
+        <v>68.219141463946926</v>
       </c>
       <c r="V9">
-        <v>0.2590486111111111</v>
+        <v>0.31711805555555556</v>
       </c>
       <c r="W9">
-        <v>0.3190486111111111</v>
+        <v>0.37711805555555555</v>
       </c>
       <c r="X9">
-        <v>0.28904861111111108</v>
+        <v>0.34711805555555558</v>
       </c>
       <c r="Y9">
+        <v>109.25</v>
+      </c>
+      <c r="Z9">
         <v>109.45</v>
       </c>
-      <c r="Z9">
-        <v>109.75</v>
-      </c>
       <c r="AA9">
-        <v>109.6</v>
+        <v>109.35</v>
       </c>
       <c r="AB9">
-        <v>1.0144727478456428</v>
+        <v>1.053006338945103</v>
       </c>
       <c r="AC9">
-        <v>0.94389865272445872</v>
+        <v>1.0056403990270071</v>
       </c>
       <c r="AD9">
-        <v>0.97915473171139189</v>
+        <v>1.0293094701950247</v>
       </c>
       <c r="AE9" t="s">
         <v>40</v>
@@ -2771,7 +2756,7 @@
         <v>100.324</v>
       </c>
       <c r="O10">
-        <v>9.3111111111111118</v>
+        <v>9.2944444444444443</v>
       </c>
       <c r="P10">
         <v>1.4150252948365027E-2</v>
@@ -2783,40 +2768,40 @@
         <v>3.5499999999999998E-3</v>
       </c>
       <c r="S10">
-        <v>77.678411118360543</v>
+        <v>76.029712511242948</v>
       </c>
       <c r="T10">
-        <v>70.846917449367965</v>
+        <v>70.884343913924937</v>
       </c>
       <c r="U10">
-        <v>74.25684757708585</v>
+        <v>73.453734568409757</v>
       </c>
       <c r="V10">
-        <v>0.52227777777777784</v>
+        <v>0.55574999999999997</v>
       </c>
       <c r="W10">
-        <v>0.58227777777777778</v>
+        <v>0.61575000000000002</v>
       </c>
       <c r="X10">
-        <v>0.55227777777777776</v>
+        <v>0.58574999999999999</v>
       </c>
       <c r="Y10">
-        <v>101.05</v>
+        <v>100.9</v>
       </c>
       <c r="Z10">
-        <v>101.65</v>
+        <v>101.35</v>
       </c>
       <c r="AA10">
-        <v>101.35</v>
+        <v>101.125</v>
       </c>
       <c r="AB10">
-        <v>1.3290618889613832</v>
+        <v>1.3460471251124295</v>
       </c>
       <c r="AC10">
-        <v>1.2607469522714574</v>
+        <v>1.2945934391392493</v>
       </c>
       <c r="AD10">
-        <v>1.2948462535486363</v>
+        <v>1.3202873456840976</v>
       </c>
       <c r="AE10" t="s">
         <v>40</v>
@@ -2869,7 +2854,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>1.3472222222222223</v>
+        <v>1.3305555555555555</v>
       </c>
       <c r="P11">
         <v>1.0019999999999999E-2</v>
@@ -2881,40 +2866,40 @@
         <v>-5.2500000000000003E-3</v>
       </c>
       <c r="S11">
-        <v>51.401451824555707</v>
+        <v>49.54743319548237</v>
       </c>
       <c r="T11">
-        <v>48.415874761728759</v>
+        <v>42.739685799644235</v>
       </c>
       <c r="U11">
-        <v>49.908404209688854</v>
+        <v>46.142222458956795</v>
       </c>
       <c r="V11">
-        <v>6.711805555555557E-2</v>
+        <v>0.14131944444444444</v>
       </c>
       <c r="W11">
-        <v>0.12711805555555555</v>
+        <v>0.20131944444444444</v>
       </c>
       <c r="X11">
-        <v>9.7118055555555569E-2</v>
+        <v>0.17131944444444444</v>
       </c>
       <c r="Y11">
-        <v>100.52</v>
+        <v>100.44</v>
       </c>
       <c r="Z11">
-        <v>100.56</v>
+        <v>100.53</v>
       </c>
       <c r="AA11">
-        <v>100.53999999999999</v>
+        <v>100.485</v>
       </c>
       <c r="AB11">
-        <v>0.61113257380111263</v>
+        <v>0.66679377639926818</v>
       </c>
       <c r="AC11">
-        <v>0.58127680317284314</v>
+        <v>0.59871630244088681</v>
       </c>
       <c r="AD11">
-        <v>0.59620209765244414</v>
+        <v>0.63274166903401241</v>
       </c>
       <c r="AE11" t="s">
         <v>40</v>
@@ -2967,7 +2952,7 @@
         <v>100.369</v>
       </c>
       <c r="O12">
-        <v>0.87777777777777777</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="P12">
         <v>8.8921964786545012E-3</v>
@@ -2979,40 +2964,40 @@
         <v>-1.0249999999999999E-3</v>
       </c>
       <c r="S12">
-        <v>29.877918548498144</v>
+        <v>29.870813712645983</v>
       </c>
       <c r="T12">
-        <v>19.605901757381464</v>
+        <v>25.211087953875079</v>
       </c>
       <c r="U12">
-        <v>24.739615204409233</v>
+        <v>27.540487867135354</v>
       </c>
       <c r="V12">
-        <v>1.4833333333333337E-2</v>
+        <v>6.1111111111111137E-2</v>
       </c>
       <c r="W12">
-        <v>7.4833333333333335E-2</v>
+        <v>0.12111111111111114</v>
       </c>
       <c r="X12">
-        <v>4.4833333333333336E-2</v>
+        <v>9.1111111111111143E-2</v>
       </c>
       <c r="Y12">
-        <v>100.54</v>
+        <v>100.49</v>
       </c>
       <c r="Z12">
-        <v>100.63</v>
+        <v>100.53</v>
       </c>
       <c r="AA12">
-        <v>100.58500000000001</v>
+        <v>100.50999999999999</v>
       </c>
       <c r="AB12">
-        <v>0.34361251881831478</v>
+        <v>0.38981924823757097</v>
       </c>
       <c r="AC12">
-        <v>0.24089235090714797</v>
+        <v>0.34322199064986192</v>
       </c>
       <c r="AD12">
-        <v>0.29222948537742566</v>
+        <v>0.36651598978246469</v>
       </c>
       <c r="AE12" t="s">
         <v>106</v>
@@ -3065,7 +3050,7 @@
         <v>100.057</v>
       </c>
       <c r="O13">
-        <v>0.49166666666666664</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="P13">
         <v>1.9850358815562616E-2</v>
@@ -3077,40 +3062,40 @@
         <v>9.6249999999999999E-3</v>
       </c>
       <c r="S13">
-        <v>34.556124551383796</v>
+        <v>40.731709907047694</v>
       </c>
       <c r="T13">
-        <v>26.470333660945609</v>
+        <v>26.072466553550385</v>
       </c>
       <c r="U13">
-        <v>30.512018056016593</v>
+        <v>33.398153707230612</v>
       </c>
       <c r="V13">
-        <v>-4.8236666666666671E-2</v>
+        <v>-4.2470000000000001E-2</v>
       </c>
       <c r="W13">
-        <v>1.1763333333333327E-2</v>
+        <v>1.753E-2</v>
       </c>
       <c r="X13">
-        <v>-1.8236666666666672E-2</v>
+        <v>-1.2470000000000002E-2</v>
       </c>
       <c r="Y13">
-        <v>101.01</v>
+        <v>100.95</v>
       </c>
       <c r="Z13">
-        <v>101.05</v>
+        <v>101.02</v>
       </c>
       <c r="AA13">
-        <v>101.03</v>
+        <v>100.985</v>
       </c>
       <c r="AB13">
-        <v>0.32732457884717125</v>
+        <v>0.39484709907047694</v>
       </c>
       <c r="AC13">
-        <v>0.24646666994278946</v>
+        <v>0.24825466553550382</v>
       </c>
       <c r="AD13">
-        <v>0.28688351389349925</v>
+        <v>0.32151153707230612</v>
       </c>
       <c r="AE13" t="s">
         <v>40</v>
@@ -3163,7 +3148,7 @@
         <v>100.26</v>
       </c>
       <c r="O14">
-        <v>2.9916666666666667</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="P14">
         <v>2.6045598125088939E-2</v>
@@ -3175,40 +3160,40 @@
         <v>1.1725000000000001E-2</v>
       </c>
       <c r="S14">
-        <v>59.274634008488135</v>
+        <v>57.200785035676347</v>
       </c>
       <c r="T14">
-        <v>54.353391454891629</v>
+        <v>53.893208215467162</v>
       </c>
       <c r="U14">
-        <v>56.812825572408478</v>
+        <v>55.546462934846033</v>
       </c>
       <c r="V14">
-        <v>0.18947916666666667</v>
+        <v>0.26643749999999999</v>
       </c>
       <c r="W14">
-        <v>0.24947916666666667</v>
+        <v>0.32643750000000005</v>
       </c>
       <c r="X14">
-        <v>0.21947916666666667</v>
+        <v>0.29643750000000002</v>
       </c>
       <c r="Y14">
-        <v>105.4</v>
+        <v>105.2</v>
       </c>
       <c r="Z14">
-        <v>105.55</v>
+        <v>105.3</v>
       </c>
       <c r="AA14">
-        <v>105.47499999999999</v>
+        <v>105.25</v>
       </c>
       <c r="AB14">
-        <v>0.81222550675154803</v>
+        <v>0.86844535035676351</v>
       </c>
       <c r="AC14">
-        <v>0.76301308121558298</v>
+        <v>0.83536958215467161</v>
       </c>
       <c r="AD14">
-        <v>0.78760742239075143</v>
+        <v>0.85190212934846032</v>
       </c>
       <c r="AE14" t="s">
         <v>106</v>
@@ -3261,7 +3246,7 @@
         <v>100.06400000000001</v>
       </c>
       <c r="O15">
-        <v>0.51111111111111107</v>
+        <v>0.49444444444444446</v>
       </c>
       <c r="P15">
         <v>2.4776009334897025E-2</v>
@@ -3273,40 +3258,40 @@
         <v>1.7174999999999999E-2</v>
       </c>
       <c r="S15">
-        <v>35.208311607591433</v>
+        <v>33.505577489409369</v>
       </c>
       <c r="T15">
-        <v>27.454584877210614</v>
+        <v>29.496341188370923</v>
       </c>
       <c r="U15">
-        <v>31.330320169821</v>
+        <v>31.500661092381449</v>
       </c>
       <c r="V15">
-        <v>-4.5666666666666675E-2</v>
+        <v>-4.0548888888888891E-2</v>
       </c>
       <c r="W15">
-        <v>1.4333333333333328E-2</v>
+        <v>1.945111111111111E-2</v>
       </c>
       <c r="X15">
-        <v>-1.5666666666666676E-2</v>
+        <v>-1.0548888888888892E-2</v>
       </c>
       <c r="Y15">
-        <v>101.09</v>
+        <v>101.06</v>
       </c>
       <c r="Z15">
-        <v>101.13</v>
+        <v>101.08</v>
       </c>
       <c r="AA15">
-        <v>101.11</v>
+        <v>101.07</v>
       </c>
       <c r="AB15">
-        <v>0.3364164494092477</v>
+        <v>0.32450688600520483</v>
       </c>
       <c r="AC15">
-        <v>0.25887918210543948</v>
+        <v>0.28441452299482034</v>
       </c>
       <c r="AD15">
-        <v>0.29763653503154336</v>
+        <v>0.3044577220349256</v>
       </c>
       <c r="AE15" t="s">
         <v>40</v>
@@ -3359,7 +3344,7 @@
         <v>100.246</v>
       </c>
       <c r="O16">
-        <v>7.1694444444444443</v>
+        <v>7.1527777777777777</v>
       </c>
       <c r="P16">
         <v>1.2175414431044345E-2</v>
@@ -3371,40 +3356,40 @@
         <v>2.8000000000000004E-3</v>
       </c>
       <c r="S16">
-        <v>74.644300888888878</v>
+        <v>77.520110562415695</v>
       </c>
       <c r="T16">
-        <v>72.377377888888887</v>
+        <v>73.786488999999989</v>
       </c>
       <c r="U16">
-        <v>73.510342888888886</v>
+        <v>75.680415049375469</v>
       </c>
       <c r="V16">
-        <v>0.42054861111111108</v>
+        <v>0.45937500000000003</v>
       </c>
       <c r="W16">
-        <v>0.48054861111111108</v>
+        <v>0.51937499999999992</v>
       </c>
       <c r="X16">
-        <v>0.45054861111111111</v>
+        <v>0.489375</v>
       </c>
       <c r="Y16">
-        <v>100.35</v>
+        <v>99.9</v>
       </c>
       <c r="Z16">
-        <v>100.5</v>
+        <v>100.15</v>
       </c>
       <c r="AA16">
-        <v>100.425</v>
+        <v>100.02500000000001</v>
       </c>
       <c r="AB16">
-        <v>1.1969916199999999</v>
+        <v>1.2645761056241569</v>
       </c>
       <c r="AC16">
-        <v>1.1743223899999999</v>
+        <v>1.2272398899999999</v>
       </c>
       <c r="AD16">
-        <v>1.1856520399999999</v>
+        <v>1.2461791504937547</v>
       </c>
       <c r="AE16" t="s">
         <v>40</v>
@@ -3457,7 +3442,7 @@
         <v>100.465</v>
       </c>
       <c r="O17">
-        <v>4.5750000000000002</v>
+        <v>4.5583333333333336</v>
       </c>
       <c r="P17">
         <v>2.4702553304086123E-2</v>
@@ -3469,40 +3454,40 @@
         <v>#VALUE!</v>
       </c>
       <c r="S17">
-        <v>66.59507608577681</v>
+        <v>67.232698483783508</v>
       </c>
       <c r="T17">
-        <v>60.134445718684013</v>
+        <v>59.645190904692704</v>
       </c>
       <c r="U17">
-        <v>63.361924756602953</v>
+        <v>63.435046535026117</v>
       </c>
       <c r="V17">
-        <v>0.2855625</v>
+        <v>0.33902083333333333</v>
       </c>
       <c r="W17">
-        <v>0.34556249999999999</v>
+        <v>0.39902083333333332</v>
       </c>
       <c r="X17">
-        <v>0.31556249999999997</v>
+        <v>0.36902083333333335</v>
       </c>
       <c r="Y17">
-        <v>106.75</v>
+        <v>106.45</v>
       </c>
       <c r="Z17">
-        <v>107.05</v>
+        <v>106.8</v>
       </c>
       <c r="AA17">
-        <v>106.9</v>
+        <v>106.625</v>
       </c>
       <c r="AB17">
-        <v>0.98151326085776813</v>
+        <v>1.0413478181711684</v>
       </c>
       <c r="AC17">
-        <v>0.91690695718684012</v>
+        <v>0.96547274238026037</v>
       </c>
       <c r="AD17">
-        <v>0.94918174756602947</v>
+        <v>1.0033712986835945</v>
       </c>
       <c r="AE17" t="s">
         <v>40</v>
@@ -3555,7 +3540,7 @@
         <v>100.337</v>
       </c>
       <c r="O18">
-        <v>1.3638888888888889</v>
+        <v>1.3472222222222223</v>
       </c>
       <c r="P18">
         <v>2.074807432443967E-3</v>
@@ -3567,40 +3552,40 @@
         <v>-4.9499999999999995E-3</v>
       </c>
       <c r="S18">
-        <v>59.653269997277405</v>
+        <v>62.562067280583008</v>
       </c>
       <c r="T18">
-        <v>44.7600208994849</v>
+        <v>52.7325089044148</v>
       </c>
       <c r="U18">
-        <v>52.20014886847698</v>
+        <v>57.644481754617807</v>
       </c>
       <c r="V18">
-        <v>6.8659722222222219E-2</v>
+        <v>0.1434027777777778</v>
       </c>
       <c r="W18">
-        <v>0.12865972222222222</v>
+        <v>0.20340277777777779</v>
       </c>
       <c r="X18">
-        <v>9.8659722222222218E-2</v>
+        <v>0.17340277777777779</v>
       </c>
       <c r="Y18">
+        <v>99.27</v>
+      </c>
+      <c r="Z18">
         <v>99.4</v>
       </c>
-      <c r="Z18">
-        <v>99.6</v>
-      </c>
       <c r="AA18">
-        <v>99.5</v>
+        <v>99.335000000000008</v>
       </c>
       <c r="AB18">
-        <v>0.69519242219499622</v>
+        <v>0.79902345058360791</v>
       </c>
       <c r="AC18">
-        <v>0.54625993121707117</v>
+        <v>0.70072786682192578</v>
       </c>
       <c r="AD18">
-        <v>0.620661210906992</v>
+        <v>0.74984759532395584</v>
       </c>
       <c r="AE18" t="s">
         <v>40</v>
@@ -3653,7 +3638,7 @@
         <v>100.35300000000001</v>
       </c>
       <c r="O19">
-        <v>0.10833333333333334</v>
+        <v>9.166666666666666E-2</v>
       </c>
       <c r="P19">
         <v>7.8501129676108693E-3</v>
@@ -3665,40 +3650,40 @@
         <v>4.8500000000000001E-3</v>
       </c>
       <c r="S19">
-        <v>53.395866802502908</v>
+        <v>45.740926390744072</v>
       </c>
       <c r="T19">
-        <v>24.439816888423934</v>
+        <v>22.705007536856904</v>
       </c>
       <c r="U19">
-        <v>38.915688233547598</v>
+        <v>34.22182487167639</v>
       </c>
       <c r="V19">
-        <v>-8.2123333333333326E-2</v>
+        <v>-8.0343333333333336E-2</v>
       </c>
       <c r="W19">
-        <v>-2.2123333333333335E-2</v>
+        <v>-2.0343333333333335E-2</v>
       </c>
       <c r="X19">
-        <v>-5.2123333333333334E-2</v>
+        <v>-5.034333333333333E-2</v>
       </c>
       <c r="Y19">
         <v>100.04</v>
       </c>
       <c r="Z19">
-        <v>100.07</v>
+        <v>100.06</v>
       </c>
       <c r="AA19">
-        <v>100.05500000000001</v>
+        <v>100.05000000000001</v>
       </c>
       <c r="AB19">
-        <v>0.48183533469169582</v>
+        <v>0.40706593057410739</v>
       </c>
       <c r="AC19">
-        <v>0.19227483555090602</v>
+        <v>0.1767067420352357</v>
       </c>
       <c r="AD19">
-        <v>0.33703354900214266</v>
+        <v>0.29187491538343058</v>
       </c>
       <c r="AE19" t="s">
         <v>148</v>
@@ -3751,7 +3736,7 @@
         <v>100.20100000000001</v>
       </c>
       <c r="O20">
-        <v>3.1083333333333334</v>
+        <v>3.0916666666666668</v>
       </c>
       <c r="P20">
         <v>1.0950143159872435E-2</v>
@@ -3763,40 +3748,40 @@
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="S20">
-        <v>57.051633451269623</v>
+        <v>59.226695797437891</v>
       </c>
       <c r="T20">
-        <v>48.931046849345869</v>
+        <v>47.759662204091775</v>
       </c>
       <c r="U20">
-        <v>52.987997178708248</v>
+        <v>53.48654512145454</v>
       </c>
       <c r="V20">
-        <v>0.19677083333333334</v>
+        <v>0.27162500000000001</v>
       </c>
       <c r="W20">
-        <v>0.25677083333333334</v>
+        <v>0.331625</v>
       </c>
       <c r="X20">
-        <v>0.22677083333333334</v>
+        <v>0.30162499999999998</v>
       </c>
       <c r="Y20">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="Z20">
-        <v>101.25</v>
+        <v>101.05</v>
       </c>
       <c r="AA20">
-        <v>101.125</v>
+        <v>100.875</v>
       </c>
       <c r="AB20">
-        <v>0.7972871678460296</v>
+        <v>0.89389195797437881</v>
       </c>
       <c r="AC20">
-        <v>0.71608130182679208</v>
+        <v>0.77922162204091772</v>
       </c>
       <c r="AD20">
-        <v>0.75665080512041583</v>
+        <v>0.83649045121454546</v>
       </c>
       <c r="AE20" t="s">
         <v>148</v>
@@ -3849,7 +3834,7 @@
         <v>101.137</v>
       </c>
       <c r="O21">
-        <v>8.5833333333333339</v>
+        <v>8.5666666666666664</v>
       </c>
       <c r="P21">
         <v>1.377509024618267E-2</v>
@@ -3861,40 +3846,40 @@
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="S21">
-        <v>66.154759841019498</v>
+        <v>71.115406381291365</v>
       </c>
       <c r="T21">
-        <v>62.518356220345147</v>
+        <v>65.612152955254004</v>
       </c>
       <c r="U21">
-        <v>64.335022375019236</v>
+        <v>68.360271352584562</v>
       </c>
       <c r="V21">
-        <v>0.48770833333333335</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="W21">
-        <v>0.54770833333333335</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="X21">
-        <v>0.51770833333333333</v>
+        <v>0.55299999999999994</v>
       </c>
       <c r="Y21">
-        <v>102.6</v>
+        <v>101.9</v>
       </c>
       <c r="Z21">
-        <v>102.9</v>
+        <v>102.35</v>
       </c>
       <c r="AA21">
-        <v>102.75</v>
+        <v>102.125</v>
       </c>
       <c r="AB21">
-        <v>1.1792559317435283</v>
+        <v>1.2641540638129136</v>
       </c>
       <c r="AC21">
-        <v>1.1428918955367848</v>
+        <v>1.2091215295525399</v>
       </c>
       <c r="AD21">
-        <v>1.1610585570835257</v>
+        <v>1.2366027135258455</v>
       </c>
       <c r="AE21" t="s">
         <v>40</v>
@@ -3947,7 +3932,7 @@
         <v>100.087</v>
       </c>
       <c r="O22">
-        <v>5.5750000000000002</v>
+        <v>5.5583333333333336</v>
       </c>
       <c r="P22">
         <v>8.6006040449016063E-3</v>
@@ -3959,40 +3944,40 @@
         <v>1.6250000000000001E-3</v>
       </c>
       <c r="S22">
-        <v>64.379468589519703</v>
+        <v>63.529656169950954</v>
       </c>
       <c r="T22">
-        <v>58.798250471452931</v>
+        <v>58.852363546108286</v>
       </c>
       <c r="U22">
-        <v>61.586343805171893</v>
+        <v>61.18924822579109</v>
       </c>
       <c r="V22">
-        <v>0.34018749999999998</v>
+        <v>0.38652083333333331</v>
       </c>
       <c r="W22">
-        <v>0.40018749999999997</v>
+        <v>0.44652083333333337</v>
       </c>
       <c r="X22">
-        <v>0.37018749999999995</v>
+        <v>0.41652083333333334</v>
       </c>
       <c r="Y22">
-        <v>99.25</v>
+        <v>99.05</v>
       </c>
       <c r="Z22">
-        <v>99.55</v>
+        <v>99.3</v>
       </c>
       <c r="AA22">
-        <v>99.4</v>
+        <v>99.174999999999997</v>
       </c>
       <c r="AB22">
-        <v>1.013982185895197</v>
+        <v>1.0518173950328429</v>
       </c>
       <c r="AC22">
-        <v>0.95817000471452929</v>
+        <v>1.0050444687944162</v>
       </c>
       <c r="AD22">
-        <v>0.98605093805171884</v>
+        <v>1.0284133155912443</v>
       </c>
       <c r="AE22" t="s">
         <v>40</v>
@@ -4045,7 +4030,7 @@
         <v>100.057</v>
       </c>
       <c r="O23">
-        <v>2.2999999999999998</v>
+        <v>2.2833333333333332</v>
       </c>
       <c r="P23">
         <v>3.4373979354317165E-2</v>
@@ -4057,40 +4042,40 @@
         <v>1.9400000000000001E-2</v>
       </c>
       <c r="S23">
-        <v>98.434255952588941</v>
+        <v>94.235195574148591</v>
       </c>
       <c r="T23">
-        <v>60.18660929456594</v>
+        <v>81.317885103581062</v>
       </c>
       <c r="U23">
-        <v>79.251259450624815</v>
+        <v>87.769836133307138</v>
       </c>
       <c r="V23">
-        <v>0.14624999999999999</v>
+        <v>0.23704166666666668</v>
       </c>
       <c r="W23">
-        <v>0.20624999999999999</v>
+        <v>0.29704166666666665</v>
       </c>
       <c r="X23">
-        <v>0.17624999999999999</v>
+        <v>0.26704166666666668</v>
       </c>
       <c r="Y23">
+        <v>105</v>
+      </c>
+      <c r="Z23">
+        <v>105.3</v>
+      </c>
+      <c r="AA23">
         <v>105.15</v>
       </c>
-      <c r="Z23">
-        <v>106.05</v>
-      </c>
-      <c r="AA23">
-        <v>105.6</v>
-      </c>
       <c r="AB23">
-        <v>1.1605925595258895</v>
+        <v>1.2093936224081525</v>
       </c>
       <c r="AC23">
-        <v>0.77811609294565942</v>
+        <v>1.0802205177024773</v>
       </c>
       <c r="AD23">
-        <v>0.96876259450624813</v>
+        <v>1.144740027999738</v>
       </c>
       <c r="AE23" t="s">
         <v>40</v>
@@ -4143,7 +4128,7 @@
         <v>100.30000000000001</v>
       </c>
       <c r="O24">
-        <v>2.9555555555555557</v>
+        <v>2.9388888888888891</v>
       </c>
       <c r="P24">
         <v>4.0644327100912625E-3</v>
@@ -4155,40 +4140,40 @@
         <v>2.725E-3</v>
       </c>
       <c r="S24">
-        <v>42.15520821981422</v>
+        <v>46.648420651955618</v>
       </c>
       <c r="T24">
-        <v>35.273905240940671</v>
+        <v>34.493066102545619</v>
       </c>
       <c r="U24">
-        <v>38.712236210826049</v>
+        <v>40.563540108999689</v>
       </c>
       <c r="V24">
-        <v>0.18722222222222223</v>
+        <v>0.26490277777777782</v>
       </c>
       <c r="W24">
-        <v>0.24722222222222223</v>
+        <v>0.32490277777777782</v>
       </c>
       <c r="X24">
-        <v>0.21722222222222223</v>
+        <v>0.29490277777777779</v>
       </c>
       <c r="Y24">
+        <v>99.1</v>
+      </c>
+      <c r="Z24">
         <v>99.45</v>
       </c>
-      <c r="Z24">
-        <v>99.65</v>
-      </c>
       <c r="AA24">
-        <v>99.550000000000011</v>
+        <v>99.275000000000006</v>
       </c>
       <c r="AB24">
-        <v>0.63877430442036442</v>
+        <v>0.76138698429733398</v>
       </c>
       <c r="AC24">
-        <v>0.56996127463162893</v>
+        <v>0.63983343880323396</v>
       </c>
       <c r="AD24">
-        <v>0.60434458433048266</v>
+        <v>0.7005381788677747</v>
       </c>
       <c r="AE24" t="s">
         <v>40</v>
@@ -4241,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>4.0638888888888891</v>
+        <v>4.0472222222222225</v>
       </c>
       <c r="P25">
         <v>2.0000000000000004E-2</v>
@@ -4253,40 +4238,40 @@
         <v>1.6750000000000001E-2</v>
       </c>
       <c r="S25">
-        <v>40.978328571703464</v>
+        <v>39.491641618360021</v>
       </c>
       <c r="T25">
-        <v>-17.643355489229251</v>
+        <v>26.096893472121995</v>
       </c>
       <c r="U25">
-        <v>11.453217144773337</v>
+        <v>32.783146740638557</v>
       </c>
       <c r="V25">
-        <v>0.25617361111111114</v>
+        <v>0.3147430555555556</v>
       </c>
       <c r="W25">
-        <v>0.31617361111111114</v>
+        <v>0.37474305555555559</v>
       </c>
       <c r="X25">
-        <v>0.28617361111111111</v>
+        <v>0.34474305555555562</v>
       </c>
       <c r="Y25">
-        <v>105.2</v>
+        <v>105</v>
       </c>
       <c r="Z25">
-        <v>107.65</v>
+        <v>105.55</v>
       </c>
       <c r="AA25">
-        <v>106.42500000000001</v>
+        <v>105.27500000000001</v>
       </c>
       <c r="AB25">
-        <v>0.69595689682814577</v>
+        <v>0.7396594717391558</v>
       </c>
       <c r="AC25">
-        <v>0.10974005621881862</v>
+        <v>0.60571199027677558</v>
       </c>
       <c r="AD25">
-        <v>0.40070578255884448</v>
+        <v>0.6725745229619412</v>
       </c>
       <c r="AE25" t="s">
         <v>40</v>
@@ -4339,7 +4324,7 @@
         <v>100.289</v>
       </c>
       <c r="O26">
-        <v>8.0166666666666675</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>9.1236197373802969E-3</v>
@@ -4350,41 +4335,41 @@
       <c r="R26">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="S26" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="T26" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="U26" t="e">
-        <v>#VALUE!</v>
+      <c r="S26">
+        <v>53.396179464197736</v>
+      </c>
+      <c r="T26">
+        <v>40.945849402480626</v>
+      </c>
+      <c r="U26">
+        <v>47.153949525913852</v>
       </c>
       <c r="V26">
-        <v>0.46079166666666671</v>
+        <v>0.4975</v>
       </c>
       <c r="W26">
-        <v>0.52079166666666676</v>
+        <v>0.5575</v>
       </c>
       <c r="X26">
-        <v>0.49079166666666668</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>190</v>
+        <v>0.52749999999999997</v>
+      </c>
+      <c r="Y26">
+        <v>99.15</v>
+      </c>
+      <c r="Z26">
+        <v>100.1</v>
+      </c>
+      <c r="AA26">
+        <v>99.625</v>
+      </c>
+      <c r="AB26">
+        <v>1.0614617946419773</v>
+      </c>
+      <c r="AC26">
+        <v>0.93695849402480624</v>
+      </c>
+      <c r="AD26">
+        <v>0.99903949525913849</v>
       </c>
       <c r="AE26" t="s">
         <v>40</v>
@@ -4437,7 +4422,7 @@
         <v>100.289</v>
       </c>
       <c r="O27">
-        <v>8.0166666666666675</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>9.1236197373802969E-3</v>
@@ -4448,41 +4433,41 @@
       <c r="R27">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="S27" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="T27" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="U27" t="e">
-        <v>#VALUE!</v>
+      <c r="S27">
+        <v>53.396179464197736</v>
+      </c>
+      <c r="T27">
+        <v>40.945849402480626</v>
+      </c>
+      <c r="U27">
+        <v>47.153949525913852</v>
       </c>
       <c r="V27">
-        <v>0.46079166666666671</v>
+        <v>0.4975</v>
       </c>
       <c r="W27">
-        <v>0.52079166666666676</v>
+        <v>0.5575</v>
       </c>
       <c r="X27">
-        <v>0.49079166666666668</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>190</v>
+        <v>0.52749999999999997</v>
+      </c>
+      <c r="Y27">
+        <v>99.15</v>
+      </c>
+      <c r="Z27">
+        <v>100.1</v>
+      </c>
+      <c r="AA27">
+        <v>99.625</v>
+      </c>
+      <c r="AB27">
+        <v>1.0614617946419773</v>
+      </c>
+      <c r="AC27">
+        <v>0.93695849402480624</v>
+      </c>
+      <c r="AD27">
+        <v>0.99903949525913849</v>
       </c>
       <c r="AE27" t="s">
         <v>40</v>
@@ -4493,13 +4478,13 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" t="s">
         <v>194</v>
-      </c>
-      <c r="B28" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" t="s">
-        <v>196</v>
       </c>
       <c r="D28" t="s">
         <v>73</v>
@@ -4508,96 +4493,96 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J28">
-        <v>85.233333333333334</v>
+        <v>88.3</v>
       </c>
       <c r="K28">
         <v>7</v>
       </c>
       <c r="L28">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="M28">
-        <v>8.0000000000000002E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="N28">
-        <v>100.051</v>
+        <v>100.215</v>
       </c>
       <c r="O28">
-        <v>0.24722222222222223</v>
+        <v>2.4361111111111109</v>
       </c>
       <c r="P28">
-        <v>7.9248151100804933E-3</v>
+        <v>2.7000303232092571E-3</v>
       </c>
       <c r="Q28">
-        <v>115.74815110080493</v>
+        <v>55.000303232092577</v>
       </c>
       <c r="R28">
-        <v>-3.65E-3</v>
+        <v>-2.8000000000000004E-3</v>
       </c>
       <c r="S28">
-        <v>25.908161780690552</v>
+        <v>54.848174292975152</v>
       </c>
       <c r="T28">
-        <v>17.679822407837477</v>
+        <v>52.74202046448606</v>
       </c>
       <c r="U28">
-        <v>21.792943115560611</v>
+        <v>53.79490899946763</v>
       </c>
       <c r="V28">
-        <v>-6.984555555555555E-2</v>
+        <v>0.24353472222222222</v>
       </c>
       <c r="W28">
-        <v>-9.8455555555555553E-3</v>
+        <v>0.30353472222222222</v>
       </c>
       <c r="X28">
-        <v>-3.9845555555555551E-2</v>
+        <v>0.27353472222222219</v>
       </c>
       <c r="Y28">
-        <v>100.14</v>
+        <v>98.75</v>
       </c>
       <c r="Z28">
-        <v>100.16</v>
+        <v>98.8</v>
       </c>
       <c r="AA28">
-        <v>100.15</v>
+        <v>98.775000000000006</v>
       </c>
       <c r="AB28">
-        <v>0.21923606225134995</v>
+        <v>0.82201646515197369</v>
       </c>
       <c r="AC28">
-        <v>0.13695266852281923</v>
+        <v>0.80095492686708281</v>
       </c>
       <c r="AD28">
-        <v>0.17808387560005057</v>
+        <v>0.81148381221689847</v>
       </c>
       <c r="AE28" t="s">
         <v>40</v>
       </c>
       <c r="AF28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D29" t="s">
         <v>73</v>
@@ -4606,85 +4591,85 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J29">
-        <v>88.3</v>
+        <v>87.266666666666666</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29">
-        <v>150000000</v>
+        <v>170000000</v>
       </c>
       <c r="M29">
-        <v>3.0000000000000001E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="N29">
-        <v>100.215</v>
+        <v>100.07600000000001</v>
       </c>
       <c r="O29">
-        <v>2.4527777777777779</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.7000303232092571E-3</v>
+        <v>1.6883559810782722E-2</v>
       </c>
       <c r="Q29">
-        <v>55.000303232092577</v>
+        <v>73.585598107827209</v>
       </c>
       <c r="R29">
-        <v>-2.8000000000000004E-3</v>
+        <v>9.5250000000000005E-3</v>
       </c>
       <c r="S29">
-        <v>56.995350301427592</v>
+        <v>66.021789940759959</v>
       </c>
       <c r="T29">
-        <v>46.573705681887041</v>
+        <v>61.450912888585663</v>
       </c>
       <c r="U29">
-        <v>51.779888252051485</v>
+        <v>63.735247953348392</v>
       </c>
       <c r="V29">
-        <v>0.15579861111111112</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="W29">
-        <v>0.21579861111111112</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="X29">
-        <v>0.18579861111111112</v>
+        <v>0.311</v>
       </c>
       <c r="Y29">
-        <v>98.9</v>
+        <v>102.35</v>
       </c>
       <c r="Z29">
-        <v>99.15</v>
+        <v>102.5</v>
       </c>
       <c r="AA29">
-        <v>99.025000000000006</v>
+        <v>102.425</v>
       </c>
       <c r="AB29">
-        <v>0.75575211412538712</v>
+        <v>0.97121789940759962</v>
       </c>
       <c r="AC29">
-        <v>0.65153566792998152</v>
+        <v>0.92550912888585657</v>
       </c>
       <c r="AD29">
-        <v>0.70359749363162594</v>
+        <v>0.94835247953348401</v>
       </c>
       <c r="AE29" t="s">
         <v>40</v>
       </c>
       <c r="AF29" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
@@ -4695,7 +4680,7 @@
         <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D30" t="s">
         <v>73</v>
@@ -4704,7 +4689,7 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G30" t="s">
         <v>210</v>
@@ -4716,73 +4701,73 @@
         <v>212</v>
       </c>
       <c r="J30">
-        <v>87.266666666666666</v>
+        <v>85.233333333333334</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30">
-        <v>170000000</v>
+        <v>100000000</v>
       </c>
       <c r="M30">
-        <v>1.7000000000000001E-2</v>
+        <v>2.35E-2</v>
       </c>
       <c r="N30">
-        <v>100.07600000000001</v>
+        <v>100.14400000000001</v>
       </c>
       <c r="O30">
-        <v>3.3166666666666669</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>1.6883559810782722E-2</v>
+        <v>2.3274693507708485E-2</v>
       </c>
       <c r="Q30">
-        <v>73.585598107827209</v>
+        <v>47.746935077084828</v>
       </c>
       <c r="R30">
-        <v>9.5250000000000005E-3</v>
+        <v>1.8500000000000003E-2</v>
       </c>
       <c r="S30">
-        <v>68.947743945044124</v>
+        <v>71.111242736376639</v>
       </c>
       <c r="T30">
-        <v>61.386212469921198</v>
+        <v>62.829255399901541</v>
       </c>
       <c r="U30">
-        <v>65.163945133254657</v>
+        <v>66.965895104940998</v>
       </c>
       <c r="V30">
-        <v>0.20979166666666668</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="W30">
-        <v>0.26979166666666665</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="X30">
-        <v>0.23979166666666668</v>
+        <v>0.35200000000000004</v>
       </c>
       <c r="Y30">
-        <v>102.5</v>
+        <v>105.25</v>
       </c>
       <c r="Z30">
-        <v>102.75</v>
+        <v>105.6</v>
       </c>
       <c r="AA30">
-        <v>102.625</v>
+        <v>105.425</v>
       </c>
       <c r="AB30">
-        <v>0.92926910611710789</v>
+        <v>1.0631124273637664</v>
       </c>
       <c r="AC30">
-        <v>0.85365379136587871</v>
+        <v>0.98029255399901538</v>
       </c>
       <c r="AD30">
-        <v>0.89143111799921326</v>
+        <v>1.0216589510494101</v>
       </c>
       <c r="AE30" t="s">
         <v>40</v>
       </c>
       <c r="AF30" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
@@ -4793,7 +4778,7 @@
         <v>214</v>
       </c>
       <c r="C31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D31" t="s">
         <v>73</v>
@@ -4802,7 +4787,7 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G31" t="s">
         <v>215</v>
@@ -4814,84 +4799,84 @@
         <v>217</v>
       </c>
       <c r="J31">
-        <v>85.233333333333334</v>
+        <v>97.4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>100000000</v>
+        <v>130000000</v>
       </c>
       <c r="M31">
-        <v>2.35E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="N31">
-        <v>100.14400000000001</v>
+        <v>100.604</v>
       </c>
       <c r="O31">
-        <v>4.2166666666666668</v>
+        <v>5.9555555555555557</v>
       </c>
       <c r="P31">
-        <v>2.3274693507708485E-2</v>
+        <v>2.0174859319140405E-2</v>
       </c>
       <c r="Q31">
-        <v>47.746935077084828</v>
+        <v>78.748593191404041</v>
       </c>
       <c r="R31">
-        <v>1.8500000000000003E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="S31">
-        <v>71.397497111549285</v>
+        <v>76.257505855287604</v>
       </c>
       <c r="T31">
-        <v>61.998928181363823</v>
+        <v>49.319156713954264</v>
       </c>
       <c r="U31">
-        <v>66.692584594892182</v>
+        <v>62.726994575677544</v>
       </c>
       <c r="V31">
-        <v>0.26495833333333335</v>
+        <v>0.40538888888888885</v>
       </c>
       <c r="W31">
-        <v>0.32495833333333335</v>
+        <v>0.46538888888888891</v>
       </c>
       <c r="X31">
-        <v>0.29495833333333332</v>
+        <v>0.43538888888888888</v>
       </c>
       <c r="Y31">
-        <v>105.5</v>
+        <v>105.15</v>
       </c>
       <c r="Z31">
-        <v>105.9</v>
+        <v>106.75</v>
       </c>
       <c r="AA31">
-        <v>105.7</v>
+        <v>105.95</v>
       </c>
       <c r="AB31">
-        <v>1.0089333044488262</v>
+        <v>1.1979639474417649</v>
       </c>
       <c r="AC31">
-        <v>0.91494761514697154</v>
+        <v>0.92858045602843153</v>
       </c>
       <c r="AD31">
-        <v>0.96188417928225511</v>
+        <v>1.0626588346456642</v>
       </c>
       <c r="AE31" t="s">
         <v>40</v>
       </c>
       <c r="AF31" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D32" t="s">
         <v>73</v>
@@ -4900,117 +4885,117 @@
         <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J32">
-        <v>97.4</v>
+        <v>121.66666666666667</v>
       </c>
       <c r="K32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>130000000</v>
+        <v>100000000</v>
       </c>
       <c r="M32">
-        <v>2.1000000000000001E-2</v>
+        <v>1.3999999999999999E-2</v>
       </c>
       <c r="N32">
-        <v>100.604</v>
+        <v>100.373</v>
       </c>
       <c r="O32">
-        <v>5.9722222222222223</v>
+        <v>8.8944444444444439</v>
       </c>
       <c r="P32">
-        <v>2.0174859319140405E-2</v>
+        <v>1.3598273556032601E-2</v>
       </c>
       <c r="Q32">
-        <v>78.748593191404041</v>
+        <v>79.482735560326006</v>
       </c>
       <c r="R32">
-        <v>1.23E-2</v>
+        <v>5.6499999999999996E-3</v>
       </c>
       <c r="S32">
-        <v>79.237640387309952</v>
+        <v>74.817981429101408</v>
       </c>
       <c r="T32">
-        <v>49.907976935633634</v>
+        <v>70.050718987682956</v>
       </c>
       <c r="U32">
-        <v>64.499907097963188</v>
+        <v>72.431627406657668</v>
       </c>
       <c r="V32">
-        <v>0.36104166666666665</v>
+        <v>0.53774999999999995</v>
       </c>
       <c r="W32">
-        <v>0.42104166666666665</v>
+        <v>0.59775</v>
       </c>
       <c r="X32">
-        <v>0.39104166666666662</v>
+        <v>0.56774999999999998</v>
       </c>
       <c r="Y32">
-        <v>105.25</v>
+        <v>100.7</v>
       </c>
       <c r="Z32">
-        <v>107</v>
+        <v>101.1</v>
       </c>
       <c r="AA32">
-        <v>106.125</v>
+        <v>100.9</v>
       </c>
       <c r="AB32">
-        <v>1.1834180705397661</v>
+        <v>1.3159298142910141</v>
       </c>
       <c r="AC32">
-        <v>0.89012143602300298</v>
+        <v>1.2682571898768296</v>
       </c>
       <c r="AD32">
-        <v>1.0360407376462986</v>
+        <v>1.2920662740665767</v>
       </c>
       <c r="AE32" t="s">
         <v>40</v>
       </c>
       <c r="AF32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="G33" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H33" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I33" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J33">
-        <v>121.66666666666667</v>
+        <v>121.76666666666667</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -5019,75 +5004,75 @@
         <v>100000000</v>
       </c>
       <c r="M33">
-        <v>1.3999999999999999E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="N33">
-        <v>100.373</v>
+        <v>100.044</v>
       </c>
       <c r="O33">
-        <v>8.9111111111111114</v>
+        <v>6.5166666666666666</v>
       </c>
       <c r="P33">
-        <v>1.3598273556032601E-2</v>
+        <v>2.5449609272778045E-2</v>
       </c>
       <c r="Q33">
-        <v>79.482735560326006</v>
+        <v>71.49609272778045</v>
       </c>
       <c r="R33">
-        <v>5.6499999999999996E-3</v>
+        <v>1.83E-2</v>
       </c>
       <c r="S33">
-        <v>77.089647251201995</v>
+        <v>58.764651615492866</v>
       </c>
       <c r="T33">
-        <v>70.559143134828389</v>
+        <v>52.727827129586714</v>
       </c>
       <c r="U33">
-        <v>73.819276194913769</v>
+        <v>55.742928318481574</v>
       </c>
       <c r="V33">
-        <v>0.50327777777777771</v>
+        <v>0.43074999999999997</v>
       </c>
       <c r="W33">
-        <v>0.56327777777777777</v>
+        <v>0.49074999999999996</v>
       </c>
       <c r="X33">
-        <v>0.53327777777777774</v>
+        <v>0.46074999999999999</v>
       </c>
       <c r="Y33">
-        <v>100.8</v>
+        <v>109.4</v>
       </c>
       <c r="Z33">
-        <v>101.35</v>
+        <v>109.8</v>
       </c>
       <c r="AA33">
-        <v>101.07499999999999</v>
+        <v>109.6</v>
       </c>
       <c r="AB33">
-        <v>1.3041742502897977</v>
+        <v>1.0483965161549287</v>
       </c>
       <c r="AC33">
-        <v>1.2388692091260616</v>
+        <v>0.98802827129586712</v>
       </c>
       <c r="AD33">
-        <v>1.2714705397269155</v>
+        <v>1.0181792831848158</v>
       </c>
       <c r="AE33" t="s">
         <v>40</v>
       </c>
       <c r="AF33" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B34" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C34" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D34" t="s">
         <v>131</v>
@@ -5096,96 +5081,96 @@
         <v>132</v>
       </c>
       <c r="F34" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G34" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" t="s">
+        <v>230</v>
+      </c>
+      <c r="I34" t="s">
         <v>234</v>
       </c>
-      <c r="H34" t="s">
-        <v>235</v>
-      </c>
-      <c r="I34" t="s">
-        <v>236</v>
-      </c>
       <c r="J34">
-        <v>121.76666666666667</v>
+        <v>60.866666666666667</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>100000000</v>
+        <v>120000000</v>
       </c>
       <c r="M34">
-        <v>2.5499999999999998E-2</v>
+        <v>1.95E-2</v>
       </c>
       <c r="N34">
-        <v>100.044</v>
+        <v>100.20100000000001</v>
       </c>
       <c r="O34">
-        <v>6.5333333333333332</v>
+        <v>1.5166666666666666</v>
       </c>
       <c r="P34">
-        <v>2.5449609272778045E-2</v>
+        <v>1.9074706159138477E-2</v>
       </c>
       <c r="Q34">
-        <v>71.49609272778045</v>
+        <v>46.747061591384771</v>
       </c>
       <c r="R34">
-        <v>1.83E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="S34">
-        <v>58.754494405905653</v>
+        <v>45.34207884695293</v>
       </c>
       <c r="T34">
-        <v>55.749691868969251</v>
+        <v>28.989082786593013</v>
       </c>
       <c r="U34">
-        <v>57.251270821037828</v>
+        <v>37.157255535039667</v>
       </c>
       <c r="V34">
-        <v>0.38916666666666666</v>
+        <v>0.16458333333333333</v>
       </c>
       <c r="W34">
-        <v>0.44916666666666666</v>
+        <v>0.2245833333333333</v>
       </c>
       <c r="X34">
-        <v>0.41916666666666663</v>
+        <v>0.19458333333333333</v>
       </c>
       <c r="Y34">
-        <v>109.7</v>
+        <v>101.95</v>
       </c>
       <c r="Z34">
-        <v>109.9</v>
+        <v>102.2</v>
       </c>
       <c r="AA34">
-        <v>109.80000000000001</v>
+        <v>102.075</v>
       </c>
       <c r="AB34">
-        <v>1.0067116107257232</v>
+        <v>0.6480041218028626</v>
       </c>
       <c r="AC34">
-        <v>0.97666358535635911</v>
+        <v>0.48447416119926345</v>
       </c>
       <c r="AD34">
-        <v>0.99167937487704483</v>
+        <v>0.56615588868373001</v>
       </c>
       <c r="AE34" t="s">
         <v>40</v>
       </c>
       <c r="AF34" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" t="s">
         <v>237</v>
       </c>
-      <c r="B35" t="s">
-        <v>238</v>
-      </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D35" t="s">
         <v>131</v>
@@ -5194,85 +5179,85 @@
         <v>132</v>
       </c>
       <c r="F35" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G35" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H35" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J35">
-        <v>60.866666666666667</v>
+        <v>121.73333333333333</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>120000000</v>
+        <v>150000000</v>
       </c>
       <c r="M35">
-        <v>1.95E-2</v>
+        <v>1.405E-2</v>
       </c>
       <c r="N35">
-        <v>100.20100000000001</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>1.5333333333333334</v>
+        <v>9.5055555555555564</v>
       </c>
       <c r="P35">
-        <v>1.9074706159138477E-2</v>
+        <v>1.405E-2</v>
       </c>
       <c r="Q35">
-        <v>46.747061591384771</v>
+        <v>97.5</v>
       </c>
       <c r="R35">
-        <v>1.44E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="S35">
-        <v>41.806980024133907</v>
+        <v>65.788514959425854</v>
       </c>
       <c r="T35">
-        <v>35.348138906036553</v>
+        <v>59.679049498329782</v>
       </c>
       <c r="U35">
-        <v>38.576251317632121</v>
+        <v>62.729038095744997</v>
       </c>
       <c r="V35">
-        <v>8.4333333333333343E-2</v>
+        <v>0.56525000000000003</v>
       </c>
       <c r="W35">
-        <v>0.14433333333333334</v>
+        <v>0.62525000000000008</v>
       </c>
       <c r="X35">
-        <v>0.11433333333333334</v>
+        <v>0.59525000000000006</v>
       </c>
       <c r="Y35">
-        <v>102.15</v>
+        <v>101.35</v>
       </c>
       <c r="Z35">
-        <v>102.25</v>
+        <v>101.9</v>
       </c>
       <c r="AA35">
-        <v>102.2</v>
+        <v>101.625</v>
       </c>
       <c r="AB35">
-        <v>0.53240313357467239</v>
+        <v>1.2531351495942586</v>
       </c>
       <c r="AC35">
-        <v>0.46781472239369887</v>
+        <v>1.1920404949832979</v>
       </c>
       <c r="AD35">
-        <v>0.50009584650965455</v>
+        <v>1.22254038095745</v>
       </c>
       <c r="AE35" t="s">
         <v>40</v>
       </c>
       <c r="AF35" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
@@ -5283,7 +5268,7 @@
         <v>242</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
         <v>131</v>
@@ -5292,390 +5277,390 @@
         <v>132</v>
       </c>
       <c r="F36" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G36" t="s">
+        <v>238</v>
+      </c>
+      <c r="H36" t="s">
+        <v>239</v>
+      </c>
+      <c r="I36" t="s">
         <v>243</v>
       </c>
-      <c r="H36" t="s">
-        <v>244</v>
-      </c>
-      <c r="I36" t="s">
-        <v>245</v>
-      </c>
       <c r="J36">
-        <v>121.73333333333333</v>
+        <v>48.7</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="M36">
-        <v>1.405E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>100.069</v>
       </c>
       <c r="O36">
-        <v>9.5222222222222221</v>
+        <v>3.5055555555555555</v>
       </c>
       <c r="P36">
-        <v>1.405E-2</v>
+        <v>7.3243298574365298E-3</v>
       </c>
       <c r="Q36">
-        <v>97.5</v>
+        <v>69.243298574365298</v>
       </c>
       <c r="R36">
-        <v>4.3E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="S36">
-        <v>59.146527653052651</v>
-      </c>
-      <c r="T36" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="U36" t="e">
-        <v>#VALUE!</v>
+        <v>60.450745945811114</v>
+      </c>
+      <c r="T36">
+        <v>54.603575133139103</v>
+      </c>
+      <c r="U36">
+        <v>57.525260805201029</v>
       </c>
       <c r="V36">
-        <v>0.53230555555555559</v>
+        <v>0.29025000000000001</v>
       </c>
       <c r="W36">
-        <v>0.59230555555555553</v>
+        <v>0.35025000000000001</v>
       </c>
       <c r="X36">
-        <v>0.5623055555555555</v>
+        <v>0.32025000000000003</v>
       </c>
       <c r="Y36">
-        <v>102.25</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>190</v>
+        <v>99.4</v>
+      </c>
+      <c r="Z36">
+        <v>99.6</v>
+      </c>
+      <c r="AA36">
+        <v>99.5</v>
       </c>
       <c r="AB36">
-        <v>1.153770832086082</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>190</v>
+        <v>0.92475745945811116</v>
+      </c>
+      <c r="AC36">
+        <v>0.86628575133139107</v>
+      </c>
+      <c r="AD36">
+        <v>0.89550260805201032</v>
       </c>
       <c r="AE36" t="s">
         <v>40</v>
       </c>
       <c r="AF36" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>244</v>
+      </c>
+      <c r="B37" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" t="s">
         <v>246</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>247</v>
       </c>
-      <c r="C37" t="s">
-        <v>232</v>
-      </c>
-      <c r="D37" t="s">
-        <v>131</v>
-      </c>
       <c r="E37" t="s">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="F37" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G37" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H37" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I37" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J37">
-        <v>48.7</v>
+        <v>121.66666666666667</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>100000000</v>
+        <v>130000000</v>
       </c>
       <c r="M37">
-        <v>7.4999999999999997E-3</v>
+        <v>1.3999999999999999E-2</v>
       </c>
       <c r="N37">
-        <v>100.069</v>
+        <v>100.023</v>
       </c>
       <c r="O37">
-        <v>3.5222222222222221</v>
+        <v>8.3027777777777771</v>
       </c>
       <c r="P37">
-        <v>7.3243298574365298E-3</v>
+        <v>1.3975124722365328E-2</v>
       </c>
       <c r="Q37">
-        <v>69.243298574365298</v>
+        <v>38.75124722365328</v>
       </c>
       <c r="R37">
-        <v>4.0000000000000002E-4</v>
+        <v>1.01E-2</v>
       </c>
       <c r="S37">
-        <v>61.310303636589637</v>
+        <v>53.289003999999998</v>
       </c>
       <c r="T37">
-        <v>55.505589132413746</v>
+        <v>48.159721999999995</v>
       </c>
       <c r="U37">
-        <v>58.40606611797989</v>
+        <v>50.721467000000011</v>
       </c>
       <c r="V37">
-        <v>0.22263888888888889</v>
+        <v>0.51112499999999994</v>
       </c>
       <c r="W37">
-        <v>0.28263888888888888</v>
+        <v>0.57112499999999999</v>
       </c>
       <c r="X37">
-        <v>0.25263888888888886</v>
+        <v>0.54112499999999997</v>
       </c>
       <c r="Y37">
-        <v>99.6</v>
+        <v>102.5</v>
       </c>
       <c r="Z37">
-        <v>99.8</v>
+        <v>102.9</v>
       </c>
       <c r="AA37">
-        <v>99.699999999999989</v>
+        <v>102.7</v>
       </c>
       <c r="AB37">
-        <v>0.86574192525478522</v>
+        <v>1.0740150399999999</v>
       </c>
       <c r="AC37">
-        <v>0.80769478021302632</v>
+        <v>1.0227222199999999</v>
       </c>
       <c r="AD37">
-        <v>0.83669955006868779</v>
+        <v>1.0483396700000001</v>
       </c>
       <c r="AE37" t="s">
         <v>40</v>
       </c>
       <c r="AF37" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>254</v>
+      </c>
+      <c r="B38" t="s">
+        <v>255</v>
+      </c>
+      <c r="C38" t="s">
+        <v>246</v>
+      </c>
+      <c r="D38" t="s">
+        <v>247</v>
+      </c>
+      <c r="E38" t="s">
+        <v>248</v>
+      </c>
+      <c r="F38" t="s">
         <v>249</v>
       </c>
-      <c r="B38" t="s">
+      <c r="G38" t="s">
         <v>250</v>
       </c>
-      <c r="C38" t="s">
+      <c r="H38" t="s">
         <v>251</v>
       </c>
-      <c r="D38" t="s">
-        <v>252</v>
-      </c>
-      <c r="E38" t="s">
-        <v>253</v>
-      </c>
-      <c r="F38" t="s">
-        <v>254</v>
-      </c>
-      <c r="G38" t="s">
-        <v>255</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>256</v>
       </c>
-      <c r="I38" t="s">
-        <v>257</v>
-      </c>
       <c r="J38">
-        <v>121.66666666666667</v>
+        <v>60.8</v>
       </c>
       <c r="K38">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>130000000</v>
       </c>
       <c r="M38">
-        <v>1.3999999999999999E-2</v>
+        <v>1.3000000000000001E-2</v>
       </c>
       <c r="N38">
-        <v>100.023</v>
+        <v>100.108</v>
       </c>
       <c r="O38">
-        <v>8.3194444444444446</v>
+        <v>3.3027777777777776</v>
       </c>
       <c r="P38">
-        <v>1.3975124722365328E-2</v>
+        <v>1.2775315221565215E-2</v>
       </c>
       <c r="Q38">
-        <v>38.75124722365328</v>
+        <v>37.50315221565215</v>
       </c>
       <c r="R38">
-        <v>1.01E-2</v>
+        <v>9.025E-3</v>
       </c>
       <c r="S38">
-        <v>55.665137888888893</v>
+        <v>45.559623000000002</v>
       </c>
       <c r="T38">
-        <v>49.914090888888893</v>
+        <v>29.127252999999996</v>
       </c>
       <c r="U38">
-        <v>52.785965888888889</v>
+        <v>37.329938000000006</v>
       </c>
       <c r="V38">
-        <v>0.47517361111111112</v>
+        <v>0.28112500000000001</v>
       </c>
       <c r="W38">
-        <v>0.53517361111111117</v>
+        <v>0.34112500000000001</v>
       </c>
       <c r="X38">
-        <v>0.50517361111111114</v>
+        <v>0.31112499999999998</v>
       </c>
       <c r="Y38">
-        <v>102.6</v>
+        <v>101.6</v>
       </c>
       <c r="Z38">
-        <v>103.05</v>
+        <v>102.1</v>
       </c>
       <c r="AA38">
-        <v>102.82499999999999</v>
+        <v>101.85</v>
       </c>
       <c r="AB38">
-        <v>1.0618249900000001</v>
+        <v>0.76672123000000003</v>
       </c>
       <c r="AC38">
-        <v>1.0043145200000001</v>
+        <v>0.60239752999999996</v>
       </c>
       <c r="AD38">
-        <v>1.03303327</v>
+        <v>0.68442438000000005</v>
       </c>
       <c r="AE38" t="s">
         <v>40</v>
       </c>
       <c r="AF38" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>257</v>
+      </c>
+      <c r="B39" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" t="s">
         <v>259</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" t="s">
         <v>260</v>
       </c>
-      <c r="C39" t="s">
-        <v>251</v>
-      </c>
-      <c r="D39" t="s">
-        <v>252</v>
-      </c>
-      <c r="E39" t="s">
-        <v>253</v>
-      </c>
-      <c r="F39" t="s">
-        <v>254</v>
-      </c>
       <c r="G39" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H39" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="I39" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="J39">
-        <v>60.8</v>
+        <v>85.2</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>130000000</v>
+        <v>100000000</v>
       </c>
       <c r="M39">
-        <v>1.3000000000000001E-2</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="N39">
-        <v>100.108</v>
+        <v>100.017</v>
       </c>
       <c r="O39">
-        <v>3.3194444444444446</v>
+        <v>1.5166666666666666</v>
       </c>
       <c r="P39">
-        <v>1.2775315221565215E-2</v>
+        <v>9.2748049873232624E-3</v>
       </c>
       <c r="Q39">
-        <v>37.50315221565215</v>
+        <v>140.49804987323262</v>
       </c>
       <c r="R39">
-        <v>9.025E-3</v>
+        <v>-4.7749999999999997E-3</v>
       </c>
       <c r="S39">
-        <v>39.873629222222227</v>
+        <v>83.516798504721933</v>
       </c>
       <c r="T39">
-        <v>28.480771222222224</v>
+        <v>60.112506303355673</v>
       </c>
       <c r="U39">
-        <v>34.170678222222229</v>
+        <v>71.797635595494114</v>
       </c>
       <c r="V39">
-        <v>0.20996527777777779</v>
+        <v>0.16458333333333333</v>
       </c>
       <c r="W39">
-        <v>0.26996527777777779</v>
+        <v>0.2245833333333333</v>
       </c>
       <c r="X39">
-        <v>0.23996527777777779</v>
+        <v>0.19458333333333333</v>
       </c>
       <c r="Y39">
-        <v>102</v>
+        <v>99.85</v>
       </c>
       <c r="Z39">
-        <v>102.35</v>
+        <v>100.2</v>
       </c>
       <c r="AA39">
-        <v>102.175</v>
+        <v>100.02500000000001</v>
       </c>
       <c r="AB39">
-        <v>0.63870157000000005</v>
+        <v>1.0297513183805527</v>
       </c>
       <c r="AC39">
-        <v>0.52477298999999999</v>
+        <v>0.79570839636689006</v>
       </c>
       <c r="AD39">
-        <v>0.58167206000000005</v>
+        <v>0.91255968928827447</v>
       </c>
       <c r="AE39" t="s">
         <v>40</v>
       </c>
       <c r="AF39" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B40" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C40" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
         <v>73</v>
@@ -5684,85 +5669,85 @@
         <v>55</v>
       </c>
       <c r="F40" t="s">
+        <v>260</v>
+      </c>
+      <c r="G40" t="s">
         <v>265</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>266</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>267</v>
       </c>
-      <c r="I40" t="s">
-        <v>239</v>
-      </c>
       <c r="J40">
-        <v>85.2</v>
+        <v>97.4</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>100000000</v>
+        <v>140000000</v>
       </c>
       <c r="M40">
-        <v>9.300000000000001E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="N40">
-        <v>100.017</v>
+        <v>100.02</v>
       </c>
       <c r="O40">
-        <v>1.5333333333333334</v>
+        <v>3.4916666666666667</v>
       </c>
       <c r="P40">
-        <v>9.2748049873232624E-3</v>
+        <v>4.0745394397801614E-3</v>
       </c>
       <c r="Q40">
-        <v>140.49804987323262</v>
+        <v>73.245394397801618</v>
       </c>
       <c r="R40">
-        <v>-4.7749999999999997E-3</v>
+        <v>-3.2500000000000003E-3</v>
       </c>
       <c r="S40">
-        <v>71.582029650898775</v>
+        <v>82.584746622382937</v>
       </c>
       <c r="T40">
-        <v>58.401994001779897</v>
+        <v>69.166641279202253</v>
       </c>
       <c r="U40">
-        <v>64.986571488031871</v>
+        <v>75.865723674138195</v>
       </c>
       <c r="V40">
-        <v>8.4333333333333343E-2</v>
+        <v>0.28962500000000002</v>
       </c>
       <c r="W40">
-        <v>0.14433333333333334</v>
+        <v>0.34962500000000002</v>
       </c>
       <c r="X40">
-        <v>0.11433333333333334</v>
+        <v>0.31962499999999999</v>
       </c>
       <c r="Y40">
-        <v>100.15</v>
+        <v>97.5</v>
       </c>
       <c r="Z40">
-        <v>100.35</v>
+        <v>97.95</v>
       </c>
       <c r="AA40">
-        <v>100.25</v>
+        <v>97.724999999999994</v>
       </c>
       <c r="AB40">
-        <v>0.83015362984232111</v>
+        <v>1.1454724662238294</v>
       </c>
       <c r="AC40">
-        <v>0.69835327335113229</v>
+        <v>1.0112914127920225</v>
       </c>
       <c r="AD40">
-        <v>0.76419904821365192</v>
+        <v>1.078282236741382</v>
       </c>
       <c r="AE40" t="s">
         <v>40</v>
       </c>
       <c r="AF40" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
@@ -5773,105 +5758,105 @@
         <v>269</v>
       </c>
       <c r="C41" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G41" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H41" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I41" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J41">
-        <v>97.4</v>
+        <v>60.866666666666667</v>
       </c>
       <c r="K41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>140000000</v>
+        <v>200000000</v>
       </c>
       <c r="M41">
-        <v>4.0999999999999995E-3</v>
+        <v>0.02</v>
       </c>
       <c r="N41">
-        <v>100.02</v>
+        <v>100.059</v>
       </c>
       <c r="O41">
-        <v>3.5083333333333333</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="P41">
-        <v>4.0745394397801614E-3</v>
+        <v>1.9874872001274888E-2</v>
       </c>
       <c r="Q41">
-        <v>73.245394397801618</v>
+        <v>105.24872001274888</v>
       </c>
       <c r="R41">
-        <v>-3.2500000000000003E-3</v>
+        <v>9.3500000000000007E-3</v>
       </c>
       <c r="S41">
-        <v>83.076462133039769</v>
+        <v>53.525218338089033</v>
       </c>
       <c r="T41">
-        <v>75.667192465842618</v>
+        <v>46.2096067540379</v>
       </c>
       <c r="U41">
-        <v>79.368775025689445</v>
+        <v>49.865939828724919</v>
       </c>
       <c r="V41">
-        <v>0.22177083333333333</v>
+        <v>0.12812500000000002</v>
       </c>
       <c r="W41">
-        <v>0.2817708333333333</v>
+        <v>0.18812500000000001</v>
       </c>
       <c r="X41">
-        <v>0.25177083333333333</v>
+        <v>0.15812500000000002</v>
       </c>
       <c r="Y41">
-        <v>97.7</v>
+        <v>101.58</v>
       </c>
       <c r="Z41">
-        <v>97.95</v>
+        <v>101.67</v>
       </c>
       <c r="AA41">
-        <v>97.825000000000003</v>
+        <v>101.625</v>
       </c>
       <c r="AB41">
-        <v>1.0825354546637309</v>
+        <v>0.69337718338089038</v>
       </c>
       <c r="AC41">
-        <v>1.0084427579917594</v>
+        <v>0.62022106754037898</v>
       </c>
       <c r="AD41">
-        <v>1.0454585835902277</v>
+        <v>0.65678439828724922</v>
       </c>
       <c r="AE41" t="s">
         <v>40</v>
       </c>
       <c r="AF41" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B42" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D42" t="s">
         <v>35</v>
@@ -5880,85 +5865,85 @@
         <v>74</v>
       </c>
       <c r="F42" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J42">
-        <v>60.866666666666667</v>
+        <v>73.033333333333331</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>200000000</v>
+        <v>220000000</v>
       </c>
       <c r="M42">
-        <v>0.02</v>
+        <v>1.4499999999999999E-2</v>
       </c>
       <c r="N42">
-        <v>100.059</v>
+        <v>100.029</v>
       </c>
       <c r="O42">
-        <v>1.2416666666666667</v>
+        <v>4.8888888888888893</v>
       </c>
       <c r="P42">
-        <v>1.9874872001274888E-2</v>
+        <v>1.4449193126938818E-2</v>
       </c>
       <c r="Q42">
-        <v>105.24872001274888</v>
+        <v>110.74193126938816</v>
       </c>
       <c r="R42">
-        <v>9.3500000000000007E-3</v>
+        <v>3.3750000000000004E-3</v>
       </c>
       <c r="S42">
-        <v>51.900580529636756</v>
+        <v>104.37057986298962</v>
       </c>
       <c r="T42">
-        <v>39.903031045111433</v>
+        <v>80.012903609621702</v>
       </c>
       <c r="U42">
-        <v>45.897811007515962</v>
+        <v>91.090386721618202</v>
       </c>
       <c r="V42">
-        <v>5.7354166666666671E-2</v>
+        <v>0.35472222222222222</v>
       </c>
       <c r="W42">
-        <v>0.11735416666666668</v>
+        <v>0.41472222222222221</v>
       </c>
       <c r="X42">
-        <v>8.7354166666666677E-2</v>
+        <v>0.38472222222222224</v>
       </c>
       <c r="Y42">
-        <v>101.71</v>
+        <v>100.1</v>
       </c>
       <c r="Z42">
-        <v>101.86</v>
+        <v>101.25</v>
       </c>
       <c r="AA42">
-        <v>101.785</v>
+        <v>100.675</v>
       </c>
       <c r="AB42">
-        <v>0.60635997196303426</v>
+        <v>1.4284280208521183</v>
       </c>
       <c r="AC42">
-        <v>0.48638447711778099</v>
+        <v>1.1848512583184392</v>
       </c>
       <c r="AD42">
-        <v>0.54633227674182627</v>
+        <v>1.2956260894384042</v>
       </c>
       <c r="AE42" t="s">
         <v>40</v>
       </c>
       <c r="AF42" t="s">
-        <v>280</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
@@ -5969,105 +5954,105 @@
         <v>282</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D43" t="s">
         <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="G43" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H43" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I43" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J43">
-        <v>73.033333333333331</v>
+        <v>243.5</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L43">
-        <v>220000000</v>
+        <v>125000000</v>
       </c>
       <c r="M43">
-        <v>1.4499999999999999E-2</v>
+        <v>2.8750000000000001E-2</v>
       </c>
       <c r="N43">
-        <v>100.029</v>
+        <v>100.23100000000001</v>
       </c>
       <c r="O43">
-        <v>4.9055555555555559</v>
+        <v>5.2666666666666666</v>
       </c>
       <c r="P43">
-        <v>1.4449193126938818E-2</v>
-      </c>
-      <c r="Q43">
-        <v>110.74193126938816</v>
-      </c>
-      <c r="R43">
-        <v>3.3750000000000004E-3</v>
+        <v>2.8596739142984939E-2</v>
+      </c>
+      <c r="Q43" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R43" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="S43">
-        <v>95.631494848262989</v>
-      </c>
-      <c r="T43">
-        <v>80.929652003388313</v>
-      </c>
-      <c r="U43">
-        <v>88.264972740174358</v>
+        <v>72.946823115433773</v>
+      </c>
+      <c r="T43" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U43" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="V43">
-        <v>0.30456944444444445</v>
+        <v>0.37266666666666665</v>
       </c>
       <c r="W43">
-        <v>0.36456944444444445</v>
+        <v>0.43266666666666664</v>
       </c>
       <c r="X43">
-        <v>0.33456944444444442</v>
+        <v>0.40266666666666667</v>
       </c>
       <c r="Y43">
-        <v>100.75</v>
-      </c>
-      <c r="Z43">
-        <v>101.45</v>
-      </c>
-      <c r="AA43">
-        <v>101.1</v>
+        <v>108.85</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>190</v>
       </c>
       <c r="AB43">
-        <v>1.2908843929270744</v>
-      </c>
-      <c r="AC43">
-        <v>1.1438659644783276</v>
-      </c>
-      <c r="AD43">
-        <v>1.217219171846188</v>
+        <v>1.1321348978210044</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>190</v>
       </c>
       <c r="AE43" t="s">
         <v>40</v>
       </c>
       <c r="AF43" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C44" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D44" t="s">
         <v>35</v>
@@ -6076,7 +6061,7 @@
         <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G44" t="s">
         <v>290</v>
@@ -6088,25 +6073,25 @@
         <v>292</v>
       </c>
       <c r="J44">
-        <v>243.5</v>
+        <v>365.23333333333335</v>
       </c>
       <c r="K44">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L44">
-        <v>125000000</v>
+        <v>150000000</v>
       </c>
       <c r="M44">
         <v>2.8750000000000001E-2</v>
       </c>
       <c r="N44">
-        <v>100.23100000000001</v>
+        <v>100.751</v>
       </c>
       <c r="O44">
-        <v>5.2833333333333332</v>
+        <v>16.008333333333333</v>
       </c>
       <c r="P44">
-        <v>2.8596739142984939E-2</v>
+        <v>2.8374850367677437E-2</v>
       </c>
       <c r="Q44" t="e">
         <v>#VALUE!</v>
@@ -6115,46 +6100,46 @@
         <v>#VALUE!</v>
       </c>
       <c r="S44">
-        <v>69.871732995991735</v>
+        <v>131.8314954529115</v>
       </c>
       <c r="T44">
-        <v>67.094898401607679</v>
+        <v>103.3069624980775</v>
       </c>
       <c r="U44">
-        <v>68.482728665657149</v>
+        <v>117.41094159665404</v>
       </c>
       <c r="V44">
-        <v>0.32487499999999997</v>
+        <v>0.78262500000000002</v>
       </c>
       <c r="W44">
-        <v>0.38487499999999997</v>
+        <v>0.84262499999999996</v>
       </c>
       <c r="X44">
-        <v>0.35487499999999994</v>
+        <v>0.81262500000000004</v>
       </c>
       <c r="Y44">
-        <v>109.3</v>
+        <v>110</v>
       </c>
       <c r="Z44">
-        <v>109.45</v>
+        <v>114.15</v>
       </c>
       <c r="AA44">
-        <v>109.375</v>
+        <v>112.075</v>
       </c>
       <c r="AB44">
-        <v>1.0535923299599173</v>
+        <v>2.130939954529115</v>
       </c>
       <c r="AC44">
-        <v>1.0258239840160768</v>
+        <v>1.8456946249807749</v>
       </c>
       <c r="AD44">
-        <v>1.0397022866565715</v>
+        <v>1.9867344159665403</v>
       </c>
       <c r="AE44" t="s">
         <v>40</v>
       </c>
       <c r="AF44" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
@@ -6165,7 +6150,7 @@
         <v>294</v>
       </c>
       <c r="C45" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D45" t="s">
         <v>35</v>
@@ -6174,7 +6159,7 @@
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G45" t="s">
         <v>295</v>
@@ -6186,25 +6171,25 @@
         <v>297</v>
       </c>
       <c r="J45">
-        <v>365.23333333333335</v>
+        <v>487</v>
       </c>
       <c r="K45">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L45">
-        <v>150000000</v>
+        <v>200000000</v>
       </c>
       <c r="M45">
-        <v>2.8750000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="N45">
-        <v>100.751</v>
+        <v>101.11200000000001</v>
       </c>
       <c r="O45">
-        <v>16.024999999999999</v>
+        <v>26.508333333333333</v>
       </c>
       <c r="P45">
-        <v>2.8374850367677437E-2</v>
+        <v>2.9522627701786965E-2</v>
       </c>
       <c r="Q45" t="e">
         <v>#VALUE!</v>
@@ -6213,46 +6198,46 @@
         <v>#VALUE!</v>
       </c>
       <c r="S45">
-        <v>133.55699078193618</v>
+        <v>108.89474976190228</v>
       </c>
       <c r="T45">
-        <v>94.068233079228946</v>
+        <v>88.695619126903665</v>
       </c>
       <c r="U45">
-        <v>113.50875963524368</v>
+        <v>98.672666985839854</v>
       </c>
       <c r="V45">
-        <v>0.76595000000000002</v>
+        <v>0.83594999999999997</v>
       </c>
       <c r="W45">
-        <v>0.82594999999999996</v>
+        <v>0.89595000000000002</v>
       </c>
       <c r="X45">
-        <v>0.79595000000000005</v>
+        <v>0.86595</v>
       </c>
       <c r="Y45">
-        <v>110</v>
+        <v>121.45</v>
       </c>
       <c r="Z45">
-        <v>115.8</v>
+        <v>126.25</v>
       </c>
       <c r="AA45">
-        <v>112.9</v>
+        <v>123.85</v>
       </c>
       <c r="AB45">
-        <v>2.1315199078193618</v>
+        <v>1.9548974976190228</v>
       </c>
       <c r="AC45">
-        <v>1.7366323307922895</v>
+        <v>1.7529061912690367</v>
       </c>
       <c r="AD45">
-        <v>1.9310375963524369</v>
+        <v>1.8526766698583985</v>
       </c>
       <c r="AE45" t="s">
         <v>40</v>
       </c>
       <c r="AF45" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
@@ -6263,7 +6248,7 @@
         <v>299</v>
       </c>
       <c r="C46" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D46" t="s">
         <v>35</v>
@@ -6272,7 +6257,7 @@
         <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G46" t="s">
         <v>300</v>
@@ -6284,25 +6269,25 @@
         <v>302</v>
       </c>
       <c r="J46">
-        <v>487</v>
+        <v>426.13333333333333</v>
       </c>
       <c r="K46">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L46">
-        <v>200000000</v>
+        <v>160000000</v>
       </c>
       <c r="M46">
         <v>0.03</v>
       </c>
       <c r="N46">
-        <v>101.11200000000001</v>
+        <v>102.557</v>
       </c>
       <c r="O46">
-        <v>26.524999999999999</v>
+        <v>22.022222222222222</v>
       </c>
       <c r="P46">
-        <v>2.9522627701786965E-2</v>
+        <v>2.8830225432960981E-2</v>
       </c>
       <c r="Q46" t="e">
         <v>#VALUE!</v>
@@ -6311,40 +6296,40 @@
         <v>#VALUE!</v>
       </c>
       <c r="S46">
-        <v>109.02004405686286</v>
+        <v>118.15091604355432</v>
       </c>
       <c r="T46">
-        <v>88.799103028722016</v>
+        <v>98.854064098624178</v>
       </c>
       <c r="U46">
-        <v>98.786745038866144</v>
+        <v>108.40724603968201</v>
       </c>
       <c r="V46">
-        <v>0.84161249999999999</v>
+        <v>0.8435111111111111</v>
       </c>
       <c r="W46">
-        <v>0.90161250000000004</v>
+        <v>0.90351111111111115</v>
       </c>
       <c r="X46">
-        <v>0.87161250000000001</v>
+        <v>0.87351111111111113</v>
       </c>
       <c r="Y46">
-        <v>121.3</v>
+        <v>116.6</v>
       </c>
       <c r="Z46">
-        <v>126.1</v>
+        <v>120.4</v>
       </c>
       <c r="AA46">
-        <v>123.69999999999999</v>
+        <v>118.5</v>
       </c>
       <c r="AB46">
-        <v>1.9618129405686284</v>
+        <v>2.0550202715466543</v>
       </c>
       <c r="AC46">
-        <v>1.7596035302872202</v>
+        <v>1.862051752097353</v>
       </c>
       <c r="AD46">
-        <v>1.8594799503886614</v>
+        <v>1.9575835715079313</v>
       </c>
       <c r="AE46" t="s">
         <v>40</v>
@@ -6361,7 +6346,7 @@
         <v>304</v>
       </c>
       <c r="C47" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D47" t="s">
         <v>35</v>
@@ -6370,7 +6355,7 @@
         <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G47" t="s">
         <v>305</v>
@@ -6382,25 +6367,25 @@
         <v>307</v>
       </c>
       <c r="J47">
-        <v>426.13333333333333</v>
+        <v>158.26666666666668</v>
       </c>
       <c r="K47">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="L47">
-        <v>160000000</v>
+        <v>175000000</v>
       </c>
       <c r="M47">
-        <v>0.03</v>
+        <v>2.375E-2</v>
       </c>
       <c r="N47">
-        <v>102.557</v>
+        <v>100.22200000000001</v>
       </c>
       <c r="O47">
-        <v>22.038888888888888</v>
+        <v>0.71111111111111114</v>
       </c>
       <c r="P47">
-        <v>2.8830225432960981E-2</v>
+        <v>2.3549771178287129E-2</v>
       </c>
       <c r="Q47" t="e">
         <v>#VALUE!</v>
@@ -6409,46 +6394,46 @@
         <v>#VALUE!</v>
       </c>
       <c r="S47">
-        <v>118.03258880141372</v>
-      </c>
-      <c r="T47" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="U47" t="e">
-        <v>#VALUE!</v>
+        <v>34.775472759555576</v>
+      </c>
+      <c r="T47">
+        <v>26.418450984515946</v>
+      </c>
+      <c r="U47">
+        <v>30.595478194248336</v>
       </c>
       <c r="V47">
-        <v>0.84259722222222222</v>
+        <v>1.911111111111112E-2</v>
       </c>
       <c r="W47">
-        <v>0.90259722222222216</v>
+        <v>7.9111111111111118E-2</v>
       </c>
       <c r="X47">
-        <v>0.87259722222222214</v>
+        <v>4.9111111111111119E-2</v>
       </c>
       <c r="Y47">
-        <v>116.65</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>190</v>
+        <v>101.39</v>
+      </c>
+      <c r="Z47">
+        <v>101.45</v>
+      </c>
+      <c r="AA47">
+        <v>101.42</v>
       </c>
       <c r="AB47">
-        <v>2.0529231102363594</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>190</v>
+        <v>0.39686583870666686</v>
+      </c>
+      <c r="AC47">
+        <v>0.31329562095627056</v>
+      </c>
+      <c r="AD47">
+        <v>0.35506589305359448</v>
       </c>
       <c r="AE47" t="s">
         <v>40</v>
       </c>
       <c r="AF47" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
@@ -6459,7 +6444,7 @@
         <v>309</v>
       </c>
       <c r="C48" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D48" t="s">
         <v>35</v>
@@ -6468,7 +6453,7 @@
         <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G48" t="s">
         <v>310</v>
@@ -6480,84 +6465,84 @@
         <v>312</v>
       </c>
       <c r="J48">
-        <v>158.26666666666668</v>
+        <v>85.233333333333334</v>
       </c>
       <c r="K48">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>175000000</v>
+        <v>205000000</v>
       </c>
       <c r="M48">
-        <v>2.375E-2</v>
+        <v>2.75E-2</v>
       </c>
       <c r="N48">
-        <v>100.22200000000001</v>
+        <v>100.07900000000001</v>
       </c>
       <c r="O48">
-        <v>0.72777777777777775</v>
+        <v>3.9361111111111109</v>
       </c>
       <c r="P48">
-        <v>2.3549771178287129E-2</v>
-      </c>
-      <c r="Q48" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R48" t="e">
-        <v>#VALUE!</v>
+        <v>2.7374451710115943E-2</v>
+      </c>
+      <c r="Q48">
+        <v>114.74451710115942</v>
+      </c>
+      <c r="R48">
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="S48">
-        <v>39.427586027312898</v>
+        <v>70.074745612138472</v>
       </c>
       <c r="T48">
-        <v>25.821882835067573</v>
+        <v>62.572696268429226</v>
       </c>
       <c r="U48">
-        <v>32.620763067041416</v>
+        <v>66.320331265878082</v>
       </c>
       <c r="V48">
-        <v>-9.9166666666666708E-3</v>
+        <v>0.30962499999999998</v>
       </c>
       <c r="W48">
-        <v>5.0083333333333327E-2</v>
+        <v>0.36962499999999998</v>
       </c>
       <c r="X48">
-        <v>2.0083333333333328E-2</v>
+        <v>0.33962500000000001</v>
       </c>
       <c r="Y48">
-        <v>101.41</v>
+        <v>106.55</v>
       </c>
       <c r="Z48">
-        <v>101.51</v>
+        <v>106.85</v>
       </c>
       <c r="AA48">
-        <v>101.46000000000001</v>
+        <v>106.69999999999999</v>
       </c>
       <c r="AB48">
-        <v>0.41435919360646234</v>
+        <v>1.0403724561213847</v>
       </c>
       <c r="AC48">
-        <v>0.27830216168400906</v>
+        <v>0.96535196268429224</v>
       </c>
       <c r="AD48">
-        <v>0.34629096400374748</v>
+        <v>1.0028283126587809</v>
       </c>
       <c r="AE48" t="s">
         <v>40</v>
       </c>
       <c r="AF48" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C49" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D49" t="s">
         <v>35</v>
@@ -6566,96 +6551,96 @@
         <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G49" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H49" t="s">
+        <v>311</v>
+      </c>
+      <c r="I49" t="s">
         <v>316</v>
       </c>
-      <c r="I49" t="s">
-        <v>317</v>
-      </c>
       <c r="J49">
-        <v>85.233333333333334</v>
+        <v>48.7</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>205000000</v>
+        <v>100000000</v>
       </c>
       <c r="M49">
-        <v>2.75E-2</v>
+        <v>2.35E-2</v>
       </c>
       <c r="N49">
-        <v>100.07900000000001</v>
+        <v>100.18</v>
       </c>
       <c r="O49">
-        <v>3.9527777777777779</v>
+        <v>0.93611111111111112</v>
       </c>
       <c r="P49">
-        <v>2.7374451710115943E-2</v>
+        <v>2.302380344638446E-2</v>
       </c>
       <c r="Q49">
-        <v>114.74451710115942</v>
+        <v>85.238034463844599</v>
       </c>
       <c r="R49">
-        <v>1.5900000000000001E-2</v>
+        <v>1.4499999999999999E-2</v>
       </c>
       <c r="S49">
-        <v>68.050851398238407</v>
+        <v>50.769299326461024</v>
       </c>
       <c r="T49">
-        <v>61.847746067635946</v>
+        <v>26.38775373502984</v>
       </c>
       <c r="U49">
-        <v>64.946971753328697</v>
+        <v>38.564252131829356</v>
       </c>
       <c r="V49">
-        <v>0.24954861111111112</v>
+        <v>8.2111111111111135E-2</v>
       </c>
       <c r="W49">
-        <v>0.30954861111111109</v>
+        <v>0.14211111111111113</v>
       </c>
       <c r="X49">
-        <v>0.27954861111111107</v>
+        <v>0.11211111111111113</v>
       </c>
       <c r="Y49">
-        <v>106.9</v>
+        <v>101.6</v>
       </c>
       <c r="Z49">
-        <v>107.15</v>
+        <v>101.83</v>
       </c>
       <c r="AA49">
-        <v>107.02500000000001</v>
+        <v>101.715</v>
       </c>
       <c r="AB49">
-        <v>0.96005712509349517</v>
+        <v>0.61980410437572142</v>
       </c>
       <c r="AC49">
-        <v>0.89802607178747051</v>
+        <v>0.3759886484614095</v>
       </c>
       <c r="AD49">
-        <v>0.92901832864439804</v>
+        <v>0.49775363242940474</v>
       </c>
       <c r="AE49" t="s">
         <v>40</v>
       </c>
       <c r="AF49" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C50" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D50" t="s">
         <v>35</v>
@@ -6664,96 +6649,96 @@
         <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G50" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H50" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I50" t="s">
         <v>321</v>
       </c>
       <c r="J50">
-        <v>48.7</v>
+        <v>73.066666666666663</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>100000000</v>
+        <v>110000000</v>
       </c>
       <c r="M50">
-        <v>2.35E-2</v>
+        <v>2.375E-2</v>
       </c>
       <c r="N50">
-        <v>100.18</v>
+        <v>100.152</v>
       </c>
       <c r="O50">
-        <v>0.95277777777777772</v>
+        <v>3.6972222222222224</v>
       </c>
       <c r="P50">
-        <v>2.302380344638446E-2</v>
+        <v>2.3475449396660689E-2</v>
       </c>
       <c r="Q50">
-        <v>85.238034463844599</v>
+        <v>97.504493966606887</v>
       </c>
       <c r="R50">
-        <v>1.4499999999999999E-2</v>
+        <v>1.3725000000000001E-2</v>
       </c>
       <c r="S50">
-        <v>48.820160913418363</v>
+        <v>60.587928703640216</v>
       </c>
       <c r="T50">
-        <v>29.051305336996798</v>
+        <v>56.575611331106714</v>
       </c>
       <c r="U50">
-        <v>38.926263048343671</v>
+        <v>58.580844521752859</v>
       </c>
       <c r="V50">
-        <v>2.720833333333332E-2</v>
+        <v>0.298875</v>
       </c>
       <c r="W50">
-        <v>8.7208333333333318E-2</v>
+        <v>0.358875</v>
       </c>
       <c r="X50">
-        <v>5.7208333333333319E-2</v>
+        <v>0.32887500000000003</v>
       </c>
       <c r="Y50">
-        <v>101.7</v>
+        <v>105.2</v>
       </c>
       <c r="Z50">
-        <v>101.89</v>
+        <v>105.35</v>
       </c>
       <c r="AA50">
-        <v>101.795</v>
+        <v>105.27500000000001</v>
       </c>
       <c r="AB50">
-        <v>0.54540994246751695</v>
+        <v>0.93475428703640218</v>
       </c>
       <c r="AC50">
-        <v>0.34772138670330127</v>
+        <v>0.89463111331106715</v>
       </c>
       <c r="AD50">
-        <v>0.44647096381677004</v>
+        <v>0.91468344521752865</v>
       </c>
       <c r="AE50" t="s">
         <v>40</v>
       </c>
       <c r="AF50" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
         <v>35</v>
@@ -6762,96 +6747,96 @@
         <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H51" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J51">
-        <v>73.066666666666663</v>
+        <v>97.4</v>
       </c>
       <c r="K51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L51">
-        <v>110000000</v>
+        <v>215000000</v>
       </c>
       <c r="M51">
-        <v>2.375E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="N51">
-        <v>100.152</v>
+        <v>100.261</v>
       </c>
       <c r="O51">
-        <v>3.713888888888889</v>
+        <v>6.5583333333333336</v>
       </c>
       <c r="P51">
-        <v>2.3475449396660689E-2</v>
+        <v>1.5650357139233958E-2</v>
       </c>
       <c r="Q51">
-        <v>97.504493966606887</v>
+        <v>92.003571392339566</v>
       </c>
       <c r="R51">
-        <v>1.3725000000000001E-2</v>
+        <v>6.45E-3</v>
       </c>
       <c r="S51">
-        <v>62.305401328213982</v>
+        <v>74.585582391623333</v>
       </c>
       <c r="T51">
-        <v>56.992931595363558</v>
+        <v>67.524229302007925</v>
       </c>
       <c r="U51">
-        <v>59.647537416592478</v>
+        <v>71.050321551117591</v>
       </c>
       <c r="V51">
-        <v>0.23461805555555557</v>
+        <v>0.43262499999999998</v>
       </c>
       <c r="W51">
-        <v>0.29461805555555554</v>
+        <v>0.49262499999999998</v>
       </c>
       <c r="X51">
-        <v>0.26461805555555556</v>
+        <v>0.46262500000000001</v>
       </c>
       <c r="Y51">
-        <v>105.4</v>
+        <v>102.45</v>
       </c>
       <c r="Z51">
-        <v>105.6</v>
+        <v>102.9</v>
       </c>
       <c r="AA51">
-        <v>105.5</v>
+        <v>102.67500000000001</v>
       </c>
       <c r="AB51">
-        <v>0.88767206883769545</v>
+        <v>1.2084808239162335</v>
       </c>
       <c r="AC51">
-        <v>0.83454737150919123</v>
+        <v>1.1378672930200793</v>
       </c>
       <c r="AD51">
-        <v>0.86109342972148029</v>
+        <v>1.173128215511176</v>
       </c>
       <c r="AE51" t="s">
         <v>40</v>
       </c>
       <c r="AF51" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s">
         <v>35</v>
@@ -6860,117 +6845,117 @@
         <v>55</v>
       </c>
       <c r="F52" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H52" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I52" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J52">
-        <v>97.4</v>
+        <v>121.73333333333333</v>
       </c>
       <c r="K52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L52">
-        <v>215000000</v>
+        <v>100000000</v>
       </c>
       <c r="M52">
-        <v>1.6E-2</v>
+        <v>1.1474999999999999E-2</v>
       </c>
       <c r="N52">
-        <v>100.261</v>
+        <v>100</v>
       </c>
       <c r="O52">
-        <v>6.5750000000000002</v>
+        <v>9.6972222222222229</v>
       </c>
       <c r="P52">
-        <v>1.5650357139233958E-2</v>
+        <v>1.1474999999999999E-2</v>
       </c>
       <c r="Q52">
-        <v>92.003571392339566</v>
+        <v>73.75</v>
       </c>
       <c r="R52">
-        <v>6.45E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="S52">
-        <v>75.682098240281476</v>
+        <v>74.839629661028766</v>
       </c>
       <c r="T52">
-        <v>67.875217309706613</v>
+        <v>67.589805353699091</v>
       </c>
       <c r="U52">
-        <v>71.773040246906689</v>
+        <v>71.20790063615452</v>
       </c>
       <c r="V52">
-        <v>0.39124999999999999</v>
+        <v>0.57387500000000002</v>
       </c>
       <c r="W52">
-        <v>0.45124999999999998</v>
+        <v>0.63387499999999997</v>
       </c>
       <c r="X52">
-        <v>0.42125000000000001</v>
+        <v>0.60387499999999994</v>
       </c>
       <c r="Y52">
-        <v>102.65</v>
+        <v>98.15</v>
       </c>
       <c r="Z52">
-        <v>103.15</v>
+        <v>98.8</v>
       </c>
       <c r="AA52">
-        <v>102.9</v>
+        <v>98.474999999999994</v>
       </c>
       <c r="AB52">
-        <v>1.1780709824028148</v>
+        <v>1.3522712966102877</v>
       </c>
       <c r="AC52">
-        <v>1.1000021730970662</v>
+        <v>1.2797730535369909</v>
       </c>
       <c r="AD52">
-        <v>1.1389804024690668</v>
+        <v>1.3159540063615451</v>
       </c>
       <c r="AE52" t="s">
         <v>40</v>
       </c>
       <c r="AF52" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C53" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="G53" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H53" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I53" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J53">
-        <v>121.73333333333333</v>
+        <v>121.7</v>
       </c>
       <c r="K53">
         <v>10</v>
@@ -6979,75 +6964,75 @@
         <v>100000000</v>
       </c>
       <c r="M53">
-        <v>1.1474999999999999E-2</v>
+        <v>1.25E-3</v>
       </c>
       <c r="N53">
-        <v>100</v>
+        <v>100.54900000000001</v>
       </c>
       <c r="O53">
-        <v>9.7138888888888886</v>
+        <v>4.9083333333333332</v>
       </c>
       <c r="P53">
-        <v>1.1474999999999999E-2</v>
+        <v>6.9873524188472853E-4</v>
       </c>
       <c r="Q53">
-        <v>73.75</v>
+        <v>33.737352418847287</v>
       </c>
       <c r="R53">
-        <v>4.0999999999999995E-3</v>
+        <v>-2.6750000000000003E-3</v>
       </c>
       <c r="S53">
-        <v>73.036699375862383</v>
+        <v>48.207124851826663</v>
       </c>
       <c r="T53">
-        <v>68.59920193880555</v>
+        <v>20.63196934930237</v>
       </c>
       <c r="U53">
-        <v>70.538088687688415</v>
+        <v>34.363895374547461</v>
       </c>
       <c r="V53">
-        <v>0.54140972222222228</v>
+        <v>0.35564583333333333</v>
       </c>
       <c r="W53">
-        <v>0.60140972222222222</v>
+        <v>0.41564583333333333</v>
       </c>
       <c r="X53">
-        <v>0.57140972222222219</v>
+        <v>0.38564583333333335</v>
       </c>
       <c r="Y53">
-        <v>98.6</v>
+        <v>96.45</v>
       </c>
       <c r="Z53">
-        <v>99</v>
+        <v>97.75</v>
       </c>
       <c r="AA53">
-        <v>98.8</v>
+        <v>97.1</v>
       </c>
       <c r="AB53">
-        <v>1.301776715980846</v>
+        <v>0.86771708185160001</v>
       </c>
       <c r="AC53">
-        <v>1.2574017416102776</v>
+        <v>0.59196552682635706</v>
       </c>
       <c r="AD53">
-        <v>1.2767906090991064</v>
+        <v>0.72928478707880795</v>
       </c>
       <c r="AE53" t="s">
         <v>40</v>
       </c>
       <c r="AF53" t="s">
-        <v>339</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C54" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D54" t="s">
         <v>131</v>
@@ -7056,7 +7041,7 @@
         <v>132</v>
       </c>
       <c r="F54" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G54" t="s">
         <v>344</v>
@@ -7068,73 +7053,73 @@
         <v>346</v>
       </c>
       <c r="J54">
-        <v>121.7</v>
+        <v>97.4</v>
       </c>
       <c r="K54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L54">
-        <v>100000000</v>
+        <v>160000000</v>
       </c>
       <c r="M54">
-        <v>1.25E-3</v>
+        <v>1.6250000000000001E-2</v>
       </c>
       <c r="N54">
-        <v>100.54900000000001</v>
+        <v>100.074</v>
       </c>
       <c r="O54">
-        <v>4.9249999999999998</v>
+        <v>6.3111111111111109</v>
       </c>
       <c r="P54">
-        <v>6.9873524188472853E-4</v>
+        <v>1.6150651664980763E-2</v>
       </c>
       <c r="Q54">
-        <v>33.737352418847287</v>
+        <v>50.006516649807629</v>
       </c>
       <c r="R54">
-        <v>-2.6750000000000003E-3</v>
+        <v>1.115E-2</v>
       </c>
       <c r="S54">
-        <v>54.017230463939555</v>
+        <v>52.427355209082236</v>
       </c>
       <c r="T54">
-        <v>5.6642631530657903</v>
+        <v>44.424788624219794</v>
       </c>
       <c r="U54">
-        <v>28.618225712411899</v>
+        <v>48.420360182323464</v>
       </c>
       <c r="V54">
-        <v>0.3056875</v>
+        <v>0.42149999999999999</v>
       </c>
       <c r="W54">
-        <v>0.3656875</v>
+        <v>0.48149999999999998</v>
       </c>
       <c r="X54">
-        <v>0.33568749999999997</v>
+        <v>0.45150000000000001</v>
       </c>
       <c r="Y54">
-        <v>96.4</v>
+        <v>103.95</v>
       </c>
       <c r="Z54">
-        <v>98.7</v>
+        <v>104.45</v>
       </c>
       <c r="AA54">
-        <v>97.550000000000011</v>
+        <v>104.2</v>
       </c>
       <c r="AB54">
-        <v>0.87585980463939561</v>
+        <v>0.97577355209082239</v>
       </c>
       <c r="AC54">
-        <v>0.39233013153065788</v>
+        <v>0.89574788624219792</v>
       </c>
       <c r="AD54">
-        <v>0.62186975712411896</v>
+        <v>0.93570360182323464</v>
       </c>
       <c r="AE54" t="s">
         <v>40</v>
       </c>
       <c r="AF54" t="s">
-        <v>223</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
@@ -7145,7 +7130,7 @@
         <v>348</v>
       </c>
       <c r="C55" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D55" t="s">
         <v>131</v>
@@ -7154,7 +7139,7 @@
         <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G55" t="s">
         <v>349</v>
@@ -7166,73 +7151,73 @@
         <v>351</v>
       </c>
       <c r="J55">
-        <v>97.4</v>
+        <v>109.56666666666666</v>
       </c>
       <c r="K55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L55">
-        <v>160000000</v>
+        <v>150000000</v>
       </c>
       <c r="M55">
-        <v>1.6250000000000001E-2</v>
+        <v>1.125E-2</v>
       </c>
       <c r="N55">
-        <v>100.074</v>
+        <v>100.748</v>
       </c>
       <c r="O55">
-        <v>6.3277777777777775</v>
+        <v>7.9083333333333332</v>
       </c>
       <c r="P55">
-        <v>1.6150651664980763E-2</v>
+        <v>1.0375180940955027E-2</v>
       </c>
       <c r="Q55">
-        <v>50.006516649807629</v>
+        <v>61.751809409550269</v>
       </c>
       <c r="R55">
-        <v>1.115E-2</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="S55">
-        <v>52.054817940306464</v>
+        <v>49.568302638104612</v>
       </c>
       <c r="T55">
-        <v>44.892998806780604</v>
+        <v>43.000680103697832</v>
       </c>
       <c r="U55">
-        <v>48.469321531513074</v>
+        <v>46.279799236767069</v>
       </c>
       <c r="V55">
-        <v>0.37888888888888889</v>
+        <v>0.49337500000000001</v>
       </c>
       <c r="W55">
-        <v>0.43888888888888888</v>
+        <v>0.55337499999999995</v>
       </c>
       <c r="X55">
-        <v>0.40888888888888886</v>
+        <v>0.52337499999999992</v>
       </c>
       <c r="Y55">
-        <v>104.25</v>
+        <v>100.8</v>
       </c>
       <c r="Z55">
-        <v>104.7</v>
+        <v>101.3</v>
       </c>
       <c r="AA55">
-        <v>104.47499999999999</v>
+        <v>101.05</v>
       </c>
       <c r="AB55">
-        <v>0.92943706829195349</v>
+        <v>1.019058026381046</v>
       </c>
       <c r="AC55">
-        <v>0.8578188769566949</v>
+        <v>0.95338180103697823</v>
       </c>
       <c r="AD55">
-        <v>0.89358210420401962</v>
+        <v>0.98617299236767064</v>
       </c>
       <c r="AE55" t="s">
         <v>40</v>
       </c>
       <c r="AF55" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
@@ -7243,7 +7228,7 @@
         <v>353</v>
       </c>
       <c r="C56" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D56" t="s">
         <v>131</v>
@@ -7252,7 +7237,7 @@
         <v>132</v>
       </c>
       <c r="F56" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G56" t="s">
         <v>354</v>
@@ -7264,280 +7249,280 @@
         <v>356</v>
       </c>
       <c r="J56">
-        <v>109.56666666666666</v>
+        <v>89.233333333333334</v>
       </c>
       <c r="K56">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>150000000</v>
+        <v>160000000</v>
       </c>
       <c r="M56">
-        <v>1.125E-2</v>
+        <v>0.01</v>
       </c>
       <c r="N56">
-        <v>100.748</v>
+        <v>100.19500000000001</v>
       </c>
       <c r="O56">
-        <v>7.9249999999999998</v>
+        <v>7.1833333333333336</v>
       </c>
       <c r="P56">
-        <v>1.0375180940955027E-2</v>
+        <v>9.7216830464838602E-3</v>
       </c>
       <c r="Q56">
-        <v>61.751809409550269</v>
+        <v>52.466830464838601</v>
       </c>
       <c r="R56">
-        <v>4.1999999999999997E-3</v>
+        <v>4.4749999999999998E-3</v>
       </c>
       <c r="S56">
-        <v>47.383670993444738</v>
+        <v>45.863899138400789</v>
       </c>
       <c r="T56">
-        <v>44.118563775853772</v>
+        <v>43.698343595436498</v>
       </c>
       <c r="U56">
-        <v>45.749955018747038</v>
+        <v>44.780651271286395</v>
       </c>
       <c r="V56">
-        <v>0.4564375</v>
+        <v>0.46074999999999999</v>
       </c>
       <c r="W56">
-        <v>0.51643749999999999</v>
+        <v>0.52074999999999994</v>
       </c>
       <c r="X56">
-        <v>0.48643749999999997</v>
+        <v>0.49075000000000002</v>
       </c>
       <c r="Y56">
-        <v>101.25</v>
+        <v>100.35</v>
       </c>
       <c r="Z56">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="AA56">
-        <v>101.375</v>
+        <v>100.425</v>
       </c>
       <c r="AB56">
-        <v>0.96027420993444734</v>
+        <v>0.9493889913840079</v>
       </c>
       <c r="AC56">
-        <v>0.92762313775853766</v>
+        <v>0.92773343595436497</v>
       </c>
       <c r="AD56">
-        <v>0.94393705018747032</v>
+        <v>0.938556512712864</v>
       </c>
       <c r="AE56" t="s">
         <v>40</v>
       </c>
       <c r="AF56" t="s">
-        <v>66</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C57" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="D57" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
         <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="G57" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H57" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I57" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J57">
-        <v>89.233333333333334</v>
+        <v>97.4</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L57">
-        <v>160000000</v>
+        <v>120000000</v>
       </c>
       <c r="M57">
-        <v>0.01</v>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="N57">
-        <v>100.19500000000001</v>
+        <v>100.17700000000001</v>
       </c>
       <c r="O57">
-        <v>7.2</v>
+        <v>0.50277777777777777</v>
       </c>
       <c r="P57">
-        <v>9.7216830464838602E-3</v>
+        <v>3.5252257874675429E-3</v>
       </c>
       <c r="Q57">
-        <v>52.466830464838601</v>
+        <v>30.252257874675429</v>
       </c>
       <c r="R57">
-        <v>4.4749999999999998E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="S57">
-        <v>46.870856438727529</v>
+        <v>36.372264748983127</v>
       </c>
       <c r="T57">
-        <v>44.715110408866856</v>
+        <v>20.277186405773289</v>
       </c>
       <c r="U57">
-        <v>45.792516500699712</v>
+        <v>28.319890604234338</v>
       </c>
       <c r="V57">
-        <v>0.42199999999999999</v>
+        <v>-3.9222222222222228E-2</v>
       </c>
       <c r="W57">
-        <v>0.48199999999999998</v>
+        <v>2.0777777777777777E-2</v>
       </c>
       <c r="X57">
-        <v>0.45200000000000001</v>
+        <v>-9.2222222222222254E-3</v>
       </c>
       <c r="Y57">
-        <v>100.55</v>
+        <v>100.01</v>
       </c>
       <c r="Z57">
-        <v>100.7</v>
+        <v>100.09</v>
       </c>
       <c r="AA57">
-        <v>100.625</v>
+        <v>100.05000000000001</v>
       </c>
       <c r="AB57">
-        <v>0.92070856438727533</v>
+        <v>0.354500425267609</v>
       </c>
       <c r="AC57">
-        <v>0.89915110408866861</v>
+        <v>0.19354964183551068</v>
       </c>
       <c r="AD57">
-        <v>0.90992516500699716</v>
+        <v>0.27397668382012114</v>
       </c>
       <c r="AE57" t="s">
         <v>40</v>
       </c>
       <c r="AF57" t="s">
-        <v>362</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C58" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F58" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G58" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H58" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I58" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J58">
-        <v>97.4</v>
+        <v>182.6</v>
       </c>
       <c r="K58">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L58">
-        <v>120000000</v>
+        <v>300000000</v>
       </c>
       <c r="M58">
-        <v>3.7499999999999999E-3</v>
+        <v>2.375E-2</v>
       </c>
       <c r="N58">
-        <v>100.17700000000001</v>
+        <v>100.22800000000001</v>
       </c>
       <c r="O58">
-        <v>0.51944444444444449</v>
+        <v>1.8916666666666666</v>
       </c>
       <c r="P58">
-        <v>3.5252257874675429E-3</v>
-      </c>
-      <c r="Q58">
-        <v>30.252257874675429</v>
-      </c>
-      <c r="R58">
-        <v>5.0000000000000001E-4</v>
+        <v>2.3567787015449995E-2</v>
+      </c>
+      <c r="Q58" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R58" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="S58">
-        <v>34.996767287208492</v>
+        <v>73.496714582300683</v>
       </c>
       <c r="T58">
-        <v>19.426789531691131</v>
+        <v>57.727502066152368</v>
       </c>
       <c r="U58">
-        <v>27.207202665037183</v>
+        <v>65.603250596770849</v>
       </c>
       <c r="V58">
-        <v>-4.429166666666666E-2</v>
+        <v>0.21145833333333333</v>
       </c>
       <c r="W58">
-        <v>1.5708333333333342E-2</v>
+        <v>0.2714583333333333</v>
       </c>
       <c r="X58">
-        <v>-1.4291666666666661E-2</v>
+        <v>0.24145833333333333</v>
       </c>
       <c r="Y58">
-        <v>100.02</v>
+        <v>102.6</v>
       </c>
       <c r="Z58">
-        <v>100.1</v>
+        <v>102.9</v>
       </c>
       <c r="AA58">
-        <v>100.06</v>
+        <v>102.75</v>
       </c>
       <c r="AB58">
-        <v>0.33567600620541826</v>
+        <v>0.97642547915634015</v>
       </c>
       <c r="AC58">
-        <v>0.17997622865024462</v>
+        <v>0.81873335399485703</v>
       </c>
       <c r="AD58">
-        <v>0.25778035998370519</v>
+        <v>0.89749083930104179</v>
       </c>
       <c r="AE58" t="s">
         <v>40</v>
       </c>
       <c r="AF58" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C59" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D59" t="s">
         <v>35</v>
@@ -7546,7 +7531,7 @@
         <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G59" t="s">
         <v>373</v>
@@ -7558,73 +7543,73 @@
         <v>375</v>
       </c>
       <c r="J59">
-        <v>182.6</v>
+        <v>85.2</v>
       </c>
       <c r="K59">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>300000000</v>
+        <v>250000000</v>
       </c>
       <c r="M59">
-        <v>2.375E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="N59">
-        <v>100.22800000000001</v>
+        <v>100</v>
       </c>
       <c r="O59">
-        <v>1.9083333333333334</v>
+        <v>1.2527777777777778</v>
       </c>
       <c r="P59">
-        <v>2.3567787015449995E-2</v>
-      </c>
-      <c r="Q59" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R59" t="e">
-        <v>#VALUE!</v>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="Q59">
+        <v>185.00000000000003</v>
+      </c>
+      <c r="R59">
+        <v>-6.0000000000000001E-3</v>
       </c>
       <c r="S59">
-        <v>70.901871491837838</v>
+        <v>45.807706246280461</v>
       </c>
       <c r="T59">
-        <v>57.914388872321318</v>
+        <v>41.804589996880829</v>
       </c>
       <c r="U59">
-        <v>64.40208097947658</v>
+        <v>43.805701148789105</v>
       </c>
       <c r="V59">
-        <v>0.11902083333333334</v>
+        <v>0.13159722222222223</v>
       </c>
       <c r="W59">
-        <v>0.17902083333333335</v>
+        <v>0.19159722222222222</v>
       </c>
       <c r="X59">
-        <v>0.14902083333333332</v>
+        <v>0.16159722222222223</v>
       </c>
       <c r="Y59">
-        <v>102.85</v>
+        <v>100.78</v>
       </c>
       <c r="Z59">
-        <v>103.1</v>
+        <v>100.83</v>
       </c>
       <c r="AA59">
-        <v>102.97499999999999</v>
+        <v>100.80500000000001</v>
       </c>
       <c r="AB59">
-        <v>0.8580395482517118</v>
+        <v>0.61967428468502683</v>
       </c>
       <c r="AC59">
-        <v>0.72816472205654659</v>
+        <v>0.57964312219103054</v>
       </c>
       <c r="AD59">
-        <v>0.79304164312809911</v>
+        <v>0.59965423371011328</v>
       </c>
       <c r="AE59" t="s">
         <v>40</v>
       </c>
       <c r="AF59" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
@@ -7635,7 +7620,7 @@
         <v>377</v>
       </c>
       <c r="C60" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D60" t="s">
         <v>35</v>
@@ -7644,7 +7629,7 @@
         <v>131</v>
       </c>
       <c r="F60" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G60" t="s">
         <v>378</v>
@@ -7656,67 +7641,67 @@
         <v>380</v>
       </c>
       <c r="J60">
-        <v>85.2</v>
+        <v>103.43333333333334</v>
       </c>
       <c r="K60">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L60">
-        <v>250000000</v>
+        <v>230000000</v>
       </c>
       <c r="M60">
-        <v>1.2500000000000001E-2</v>
+        <v>8.7500000000000008E-3</v>
       </c>
       <c r="N60">
-        <v>100</v>
+        <v>100.042</v>
       </c>
       <c r="O60">
-        <v>1.2694444444444444</v>
+        <v>3.1638888888888888</v>
       </c>
       <c r="P60">
-        <v>1.2500000000000001E-2</v>
+        <v>8.6973639717983393E-3</v>
       </c>
       <c r="Q60">
-        <v>185.00000000000003</v>
+        <v>133.72363971798339</v>
       </c>
       <c r="R60">
-        <v>-6.0000000000000001E-3</v>
+        <v>-4.6750000000000003E-3</v>
       </c>
       <c r="S60">
-        <v>44.317642642220953</v>
+        <v>61.835998581676733</v>
       </c>
       <c r="T60">
-        <v>40.375094736848723</v>
+        <v>58.608338011138585</v>
       </c>
       <c r="U60">
-        <v>42.345931571063801</v>
+        <v>60.22163342047552</v>
       </c>
       <c r="V60">
-        <v>5.9923611111111108E-2</v>
+        <v>0.27487499999999998</v>
       </c>
       <c r="W60">
-        <v>0.11992361111111111</v>
+        <v>0.33487499999999998</v>
       </c>
       <c r="X60">
-        <v>8.9923611111111107E-2</v>
+        <v>0.30487500000000001</v>
       </c>
       <c r="Y60">
-        <v>100.9</v>
+        <v>99.85</v>
       </c>
       <c r="Z60">
-        <v>100.95</v>
+        <v>99.95</v>
       </c>
       <c r="AA60">
-        <v>100.92500000000001</v>
+        <v>99.9</v>
       </c>
       <c r="AB60">
-        <v>0.53310003753332069</v>
+        <v>0.92323498581676733</v>
       </c>
       <c r="AC60">
-        <v>0.49367455847959835</v>
+        <v>0.89095838011138584</v>
       </c>
       <c r="AD60">
-        <v>0.51338292682174913</v>
+        <v>0.90709133420475518</v>
       </c>
       <c r="AE60" t="s">
         <v>40</v>
@@ -7733,7 +7718,7 @@
         <v>382</v>
       </c>
       <c r="C61" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D61" t="s">
         <v>35</v>
@@ -7742,7 +7727,7 @@
         <v>131</v>
       </c>
       <c r="F61" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G61" t="s">
         <v>383</v>
@@ -7754,84 +7739,84 @@
         <v>385</v>
       </c>
       <c r="J61">
-        <v>103.43333333333334</v>
+        <v>97.4</v>
       </c>
       <c r="K61">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L61">
-        <v>230000000</v>
+        <v>200000000</v>
       </c>
       <c r="M61">
-        <v>8.7500000000000008E-3</v>
+        <v>2.35E-2</v>
       </c>
       <c r="N61">
-        <v>100.042</v>
+        <v>100.054</v>
       </c>
       <c r="O61">
-        <v>3.1805555555555554</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="P61">
-        <v>8.6973639717983393E-3</v>
+        <v>2.3425192490920333E-2</v>
       </c>
       <c r="Q61">
-        <v>133.72363971798339</v>
+        <v>58.001924909203346</v>
       </c>
       <c r="R61">
-        <v>-4.6750000000000003E-3</v>
+        <v>1.7624999999999998E-2</v>
       </c>
       <c r="S61">
-        <v>67.562636863865293</v>
+        <v>64.399684508600785</v>
       </c>
       <c r="T61">
-        <v>59.548658360182252</v>
+        <v>57.89032475143636</v>
       </c>
       <c r="U61">
-        <v>63.552335769602649</v>
+        <v>61.141741953489024</v>
       </c>
       <c r="V61">
-        <v>0.20128472222222221</v>
+        <v>0.3758333333333333</v>
       </c>
       <c r="W61">
-        <v>0.26128472222222221</v>
+        <v>0.43583333333333329</v>
       </c>
       <c r="X61">
-        <v>0.23128472222222221</v>
+        <v>0.40583333333333332</v>
       </c>
       <c r="Y61">
-        <v>99.9</v>
+        <v>106.7</v>
       </c>
       <c r="Z61">
-        <v>100.15</v>
+        <v>107.05</v>
       </c>
       <c r="AA61">
-        <v>100.02500000000001</v>
+        <v>106.875</v>
       </c>
       <c r="AB61">
-        <v>0.90691109086087507</v>
+        <v>1.0498301784193411</v>
       </c>
       <c r="AC61">
-        <v>0.82677130582404468</v>
+        <v>0.98473658084769689</v>
       </c>
       <c r="AD61">
-        <v>0.86680807991824871</v>
+        <v>1.0172507528682235</v>
       </c>
       <c r="AE61" t="s">
         <v>40</v>
       </c>
       <c r="AF61" t="s">
-        <v>60</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D62" t="s">
         <v>35</v>
@@ -7840,96 +7825,96 @@
         <v>131</v>
       </c>
       <c r="F62" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G62" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H62" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I62" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J62">
-        <v>97.4</v>
+        <v>124.73333333333333</v>
       </c>
       <c r="K62">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L62">
-        <v>200000000</v>
+        <v>165000000</v>
       </c>
       <c r="M62">
-        <v>2.35E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N62">
-        <v>100.054</v>
+        <v>100.313</v>
       </c>
       <c r="O62">
-        <v>5.35</v>
+        <v>8.1722222222222225</v>
       </c>
       <c r="P62">
-        <v>2.3425192490920333E-2</v>
+        <v>1.9655886455561239E-2</v>
       </c>
       <c r="Q62">
-        <v>58.001924909203346</v>
+        <v>75.558864555612388</v>
       </c>
       <c r="R62">
-        <v>1.7624999999999998E-2</v>
+        <v>1.21E-2</v>
       </c>
       <c r="S62">
-        <v>63.958262817298994</v>
+        <v>68.179535688176003</v>
       </c>
       <c r="T62">
-        <v>58.412522058495853</v>
+        <v>61.947330284924384</v>
       </c>
       <c r="U62">
-        <v>61.183017019297004</v>
+        <v>65.05913613435834</v>
       </c>
       <c r="V62">
-        <v>0.32837499999999997</v>
+        <v>0.50524999999999998</v>
       </c>
       <c r="W62">
-        <v>0.38837499999999997</v>
+        <v>0.56525000000000003</v>
       </c>
       <c r="X62">
-        <v>0.35837499999999994</v>
+        <v>0.53525</v>
       </c>
       <c r="Y62">
-        <v>107</v>
+        <v>106.05</v>
       </c>
       <c r="Z62">
-        <v>107.3</v>
+        <v>106.55</v>
       </c>
       <c r="AA62">
-        <v>107.15</v>
+        <v>106.3</v>
       </c>
       <c r="AB62">
-        <v>0.99795762817298994</v>
+        <v>1.2170453568817601</v>
       </c>
       <c r="AC62">
-        <v>0.94250022058495853</v>
+        <v>1.1547233028492438</v>
       </c>
       <c r="AD62">
-        <v>0.97020517019296992</v>
+        <v>1.1858413613435834</v>
       </c>
       <c r="AE62" t="s">
         <v>40</v>
       </c>
       <c r="AF62" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C63" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D63" t="s">
         <v>35</v>
@@ -7938,96 +7923,96 @@
         <v>131</v>
       </c>
       <c r="F63" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G63" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H63" t="s">
-        <v>395</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s">
         <v>396</v>
       </c>
       <c r="J63">
-        <v>124.73333333333333</v>
+        <v>121.73333333333333</v>
       </c>
       <c r="K63">
         <v>10</v>
       </c>
       <c r="L63">
-        <v>165000000</v>
+        <v>125000000</v>
       </c>
       <c r="M63">
-        <v>0.02</v>
+        <v>1.2525E-2</v>
       </c>
       <c r="N63">
-        <v>100.313</v>
+        <v>100</v>
       </c>
       <c r="O63">
-        <v>8.1888888888888882</v>
+        <v>9.2166666666666668</v>
       </c>
       <c r="P63">
-        <v>1.9655886455561239E-2</v>
+        <v>1.2525E-2</v>
       </c>
       <c r="Q63">
-        <v>75.558864555612388</v>
+        <v>82.25</v>
       </c>
       <c r="R63">
-        <v>1.21E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="S63">
-        <v>64.491779763959457</v>
+        <v>71.064445262168988</v>
       </c>
       <c r="T63">
-        <v>59.54542139382739</v>
+        <v>57.574998999999991</v>
       </c>
       <c r="U63">
-        <v>62.015887182227146</v>
+        <v>64.358515999999995</v>
       </c>
       <c r="V63">
-        <v>0.46897222222222218</v>
+        <v>0.55225000000000002</v>
       </c>
       <c r="W63">
-        <v>0.52897222222222218</v>
+        <v>0.61225000000000007</v>
       </c>
       <c r="X63">
-        <v>0.49897222222222215</v>
+        <v>0.58225000000000005</v>
       </c>
       <c r="Y63">
-        <v>106.65</v>
+        <v>99.65</v>
       </c>
       <c r="Z63">
-        <v>107.05</v>
+        <v>100.8</v>
       </c>
       <c r="AA63">
-        <v>106.85</v>
+        <v>100.22499999999999</v>
       </c>
       <c r="AB63">
-        <v>1.1438900198618167</v>
+        <v>1.2928944526216899</v>
       </c>
       <c r="AC63">
-        <v>1.0944264361604961</v>
+        <v>1.15799999</v>
       </c>
       <c r="AD63">
-        <v>1.1191310940444936</v>
+        <v>1.2258351599999999</v>
       </c>
       <c r="AE63" t="s">
         <v>40</v>
       </c>
       <c r="AF63" t="s">
-        <v>397</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>397</v>
+      </c>
+      <c r="B64" t="s">
         <v>398</v>
       </c>
-      <c r="B64" t="s">
-        <v>399</v>
-      </c>
       <c r="C64" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D64" t="s">
         <v>35</v>
@@ -8036,85 +8021,85 @@
         <v>131</v>
       </c>
       <c r="F64" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G64" t="s">
+        <v>354</v>
+      </c>
+      <c r="H64" t="s">
+        <v>399</v>
+      </c>
+      <c r="I64" t="s">
         <v>400</v>
       </c>
-      <c r="H64" t="s">
-        <v>91</v>
-      </c>
-      <c r="I64" t="s">
-        <v>401</v>
-      </c>
       <c r="J64">
-        <v>121.73333333333333</v>
+        <v>122.73333333333333</v>
       </c>
       <c r="K64">
         <v>10</v>
       </c>
       <c r="L64">
-        <v>125000000</v>
+        <v>200000000</v>
       </c>
       <c r="M64">
-        <v>1.2525E-2</v>
+        <v>1.3500000000000002E-2</v>
       </c>
       <c r="N64">
-        <v>100</v>
+        <v>100.004</v>
       </c>
       <c r="O64">
-        <v>9.2333333333333325</v>
+        <v>9.9416666666666664</v>
       </c>
       <c r="P64">
-        <v>1.2525E-2</v>
+        <v>1.3494970205645919E-2</v>
       </c>
       <c r="Q64">
-        <v>82.25</v>
+        <v>71.199702056459188</v>
       </c>
       <c r="R64">
-        <v>4.3E-3</v>
+        <v>6.3749999999999996E-3</v>
       </c>
       <c r="S64">
-        <v>72.108489522741152</v>
+        <v>67.558549125715643</v>
       </c>
       <c r="T64">
-        <v>55.688808666666667</v>
+        <v>64.874256554194133</v>
       </c>
       <c r="U64">
-        <v>63.896147666666657</v>
+        <v>66.215449744287298</v>
       </c>
       <c r="V64">
-        <v>0.51858333333333329</v>
+        <v>0.58487500000000003</v>
       </c>
       <c r="W64">
-        <v>0.57858333333333334</v>
+        <v>0.64487499999999998</v>
       </c>
       <c r="X64">
-        <v>0.54858333333333331</v>
+        <v>0.61487499999999995</v>
       </c>
       <c r="Y64">
-        <v>99.85</v>
+        <v>100.55</v>
       </c>
       <c r="Z64">
-        <v>101.25</v>
+        <v>100.8</v>
       </c>
       <c r="AA64">
-        <v>100.55</v>
+        <v>100.675</v>
       </c>
       <c r="AB64">
-        <v>1.2696682285607448</v>
+        <v>1.2904604912571565</v>
       </c>
       <c r="AC64">
-        <v>1.10547142</v>
+        <v>1.2636175655419413</v>
       </c>
       <c r="AD64">
-        <v>1.1875448099999999</v>
+        <v>1.2770294974428729</v>
       </c>
       <c r="AE64" t="s">
         <v>40</v>
       </c>
       <c r="AF64" t="s">
-        <v>66</v>
+        <v>401</v>
       </c>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
@@ -8125,310 +8110,310 @@
         <v>403</v>
       </c>
       <c r="C65" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="G65" t="s">
-        <v>359</v>
+        <v>406</v>
       </c>
       <c r="H65" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="I65" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J65">
-        <v>122.73333333333333</v>
+        <v>182.63333333333333</v>
       </c>
       <c r="K65">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L65">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="M65">
-        <v>1.3500000000000002E-2</v>
+        <v>2.6249999999999999E-2</v>
       </c>
       <c r="N65">
-        <v>100.004</v>
+        <v>100.83200000000001</v>
       </c>
       <c r="O65">
-        <v>9.9583333333333339</v>
+        <v>11.308333333333334</v>
       </c>
       <c r="P65">
-        <v>1.3494970205645919E-2</v>
+        <v>2.5575176612217261E-2</v>
       </c>
       <c r="Q65">
-        <v>71.199702056459188</v>
+        <v>51.251766122172619</v>
       </c>
       <c r="R65">
-        <v>6.3749999999999996E-3</v>
+        <v>2.0449999999999999E-2</v>
       </c>
       <c r="S65">
-        <v>68.609690839007413</v>
+        <v>67.32839369148337</v>
       </c>
       <c r="T65">
-        <v>65.93564895303976</v>
+        <v>53.612198203380487</v>
       </c>
       <c r="U65">
-        <v>67.271722433538557</v>
+        <v>60.442920070994823</v>
       </c>
       <c r="V65">
-        <v>0.55302083333333341</v>
+        <v>0.64483333333333326</v>
       </c>
       <c r="W65">
-        <v>0.61302083333333335</v>
+        <v>0.70483333333333331</v>
       </c>
       <c r="X65">
-        <v>0.58302083333333332</v>
+        <v>0.67483333333333329</v>
       </c>
       <c r="Y65">
-        <v>100.75</v>
+        <v>113.3</v>
       </c>
       <c r="Z65">
-        <v>101</v>
+        <v>114.85</v>
       </c>
       <c r="AA65">
-        <v>100.875</v>
+        <v>114.07499999999999</v>
       </c>
       <c r="AB65">
-        <v>1.2691177417234074</v>
+        <v>1.348117270248167</v>
       </c>
       <c r="AC65">
-        <v>1.2423773228637309</v>
+        <v>1.2109553153671382</v>
       </c>
       <c r="AD65">
-        <v>1.2557380576687189</v>
+        <v>1.2792625340432815</v>
       </c>
       <c r="AE65" t="s">
         <v>40</v>
       </c>
       <c r="AF65" t="s">
-        <v>406</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B66" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C66" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D66" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F66" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G66" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H66" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I66" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J66">
-        <v>182.63333333333333</v>
+        <v>121.73333333333333</v>
       </c>
       <c r="K66">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L66">
         <v>100000000</v>
       </c>
       <c r="M66">
-        <v>2.6249999999999999E-2</v>
+        <v>1.03E-2</v>
       </c>
       <c r="N66">
-        <v>100.83200000000001</v>
+        <v>100</v>
       </c>
       <c r="O66">
-        <v>11.324999999999999</v>
+        <v>9.2527777777777782</v>
       </c>
       <c r="P66">
-        <v>2.5575176612217261E-2</v>
+        <v>1.03E-2</v>
       </c>
       <c r="Q66">
-        <v>51.251766122172619</v>
+        <v>70</v>
       </c>
       <c r="R66">
-        <v>2.0449999999999999E-2</v>
+        <v>3.3E-3</v>
       </c>
       <c r="S66">
-        <v>61.397215927827865</v>
+        <v>67.064788092382315</v>
       </c>
       <c r="T66">
-        <v>53.935116657391134</v>
+        <v>52.033268561184229</v>
       </c>
       <c r="U66">
-        <v>57.658047788779641</v>
+        <v>59.520832714090425</v>
       </c>
       <c r="V66">
-        <v>0.61712500000000003</v>
+        <v>0.55387500000000001</v>
       </c>
       <c r="W66">
-        <v>0.67712499999999998</v>
+        <v>0.61387500000000006</v>
       </c>
       <c r="X66">
-        <v>0.64712500000000006</v>
+        <v>0.58387500000000003</v>
       </c>
       <c r="Y66">
-        <v>114.3</v>
+        <v>98.05</v>
       </c>
       <c r="Z66">
-        <v>115.15</v>
+        <v>99.35</v>
       </c>
       <c r="AA66">
-        <v>114.72499999999999</v>
+        <v>98.699999999999989</v>
       </c>
       <c r="AB66">
-        <v>1.2610971592782787</v>
+        <v>1.2545228809238231</v>
       </c>
       <c r="AC66">
-        <v>1.1864761665739114</v>
+        <v>1.1042076856118423</v>
       </c>
       <c r="AD66">
-        <v>1.2237054778877965</v>
+        <v>1.1790833271409042</v>
       </c>
       <c r="AE66" t="s">
         <v>40</v>
       </c>
       <c r="AF66" t="s">
-        <v>223</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B67" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C67" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D67" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>421</v>
       </c>
       <c r="F67" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G67" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H67" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="I67" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J67">
-        <v>121.73333333333333</v>
+        <v>182.63333333333333</v>
       </c>
       <c r="K67">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L67">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="M67">
-        <v>1.03E-2</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="N67">
-        <v>100</v>
+        <v>101.294</v>
       </c>
       <c r="O67">
-        <v>9.2694444444444439</v>
+        <v>3.9194444444444443</v>
       </c>
       <c r="P67">
-        <v>1.03E-2</v>
-      </c>
-      <c r="Q67">
-        <v>70</v>
-      </c>
-      <c r="R67">
-        <v>3.3E-3</v>
+        <v>5.349951886562121E-3</v>
+      </c>
+      <c r="Q67" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R67" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="S67">
-        <v>66.900409885838016</v>
+        <v>37.708305124104882</v>
       </c>
       <c r="T67">
-        <v>51.946565259724423</v>
+        <v>24.720929015284877</v>
       </c>
       <c r="U67">
-        <v>59.39552788825543</v>
+        <v>31.204355303333852</v>
       </c>
       <c r="V67">
-        <v>0.52029861111111109</v>
+        <v>0.30887500000000001</v>
       </c>
       <c r="W67">
-        <v>0.58029861111111114</v>
+        <v>0.36887500000000001</v>
       </c>
       <c r="X67">
-        <v>0.55029861111111111</v>
+        <v>0.33887500000000004</v>
       </c>
       <c r="Y67">
-        <v>98.35</v>
+        <v>99.65</v>
       </c>
       <c r="Z67">
-        <v>99.65</v>
+        <v>100.15</v>
       </c>
       <c r="AA67">
-        <v>99</v>
+        <v>99.9</v>
       </c>
       <c r="AB67">
-        <v>1.2193027099694913</v>
+        <v>0.71595805124104883</v>
       </c>
       <c r="AC67">
-        <v>1.0697642637083553</v>
+        <v>0.5860842901528488</v>
       </c>
       <c r="AD67">
-        <v>1.1442538899936654</v>
+        <v>0.65091855303333856</v>
       </c>
       <c r="AE67" t="s">
         <v>40</v>
       </c>
       <c r="AF67" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>426</v>
+      </c>
+      <c r="B68" t="s">
+        <v>427</v>
+      </c>
+      <c r="C68" t="s">
+        <v>419</v>
+      </c>
+      <c r="D68" t="s">
+        <v>420</v>
+      </c>
+      <c r="E68" t="s">
+        <v>421</v>
+      </c>
+      <c r="F68" t="s">
         <v>422</v>
-      </c>
-      <c r="B68" t="s">
-        <v>423</v>
-      </c>
-      <c r="C68" t="s">
-        <v>424</v>
-      </c>
-      <c r="D68" t="s">
-        <v>425</v>
-      </c>
-      <c r="E68" t="s">
-        <v>426</v>
-      </c>
-      <c r="F68" t="s">
-        <v>427</v>
       </c>
       <c r="G68" t="s">
         <v>428</v>
@@ -8440,25 +8425,25 @@
         <v>430</v>
       </c>
       <c r="J68">
-        <v>182.63333333333333</v>
+        <v>374.36666666666667</v>
       </c>
       <c r="K68">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L68">
-        <v>150000000</v>
+        <v>125000000</v>
       </c>
       <c r="M68">
-        <v>6.2500000000000003E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N68">
-        <v>101.294</v>
+        <v>100</v>
       </c>
       <c r="O68">
-        <v>3.9361111111111109</v>
+        <v>24.266666666666666</v>
       </c>
       <c r="P68">
-        <v>5.349951886562121E-3</v>
+        <v>4.9999923196518913E-4</v>
       </c>
       <c r="Q68" t="e">
         <v>#VALUE!</v>
@@ -8467,40 +8452,40 @@
         <v>#VALUE!</v>
       </c>
       <c r="S68">
-        <v>37.231040899427228</v>
+        <v>39.615502278220305</v>
       </c>
       <c r="T68">
-        <v>24.3386529634307</v>
+        <v>26.050699556537804</v>
       </c>
       <c r="U68">
-        <v>30.774693935755753</v>
+        <v>32.775820513840912</v>
       </c>
       <c r="V68">
-        <v>0.24850694444444443</v>
+        <v>0.84463333333333335</v>
       </c>
       <c r="W68">
-        <v>0.30850694444444443</v>
+        <v>0.9046333333333334</v>
       </c>
       <c r="X68">
-        <v>0.2785069444444444</v>
+        <v>0.87463333333333337</v>
       </c>
       <c r="Y68">
-        <v>99.9</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="Z68">
-        <v>100.4</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="AA68">
-        <v>100.15</v>
+        <v>75.875</v>
       </c>
       <c r="AB68">
-        <v>0.65081735343871672</v>
+        <v>1.2707883561155364</v>
       </c>
       <c r="AC68">
-        <v>0.52189347407875142</v>
+        <v>1.1351403288987114</v>
       </c>
       <c r="AD68">
-        <v>0.58625388380200194</v>
+        <v>1.2023915384717425</v>
       </c>
       <c r="AE68" t="s">
         <v>40</v>
@@ -8517,16 +8502,16 @@
         <v>432</v>
       </c>
       <c r="C69" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D69" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E69" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F69" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G69" t="s">
         <v>433</v>
@@ -8538,73 +8523,73 @@
         <v>435</v>
       </c>
       <c r="J69">
-        <v>374.36666666666667</v>
+        <v>102.46666666666667</v>
       </c>
       <c r="K69">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="L69">
-        <v>125000000</v>
+        <v>150000000</v>
       </c>
       <c r="M69">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>100</v>
+        <v>100.434</v>
       </c>
       <c r="O69">
-        <v>24.283333333333335</v>
+        <v>2.2666666666666666</v>
       </c>
       <c r="P69">
-        <v>4.9999923196518913E-4</v>
-      </c>
-      <c r="Q69" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R69" t="e">
-        <v>#VALUE!</v>
+        <v>-5.1439549807383636E-4</v>
+      </c>
+      <c r="Q69">
+        <v>21.356045019261636</v>
+      </c>
+      <c r="R69">
+        <v>-2.65E-3</v>
       </c>
       <c r="S69">
-        <v>50.589580448050498</v>
+        <v>33.659534602969067</v>
       </c>
       <c r="T69">
-        <v>22.637674831865663</v>
+        <v>22.404706205404644</v>
       </c>
       <c r="U69">
-        <v>36.370383618862391</v>
+        <v>28.026984869914571</v>
       </c>
       <c r="V69">
-        <v>0.84820833333333334</v>
+        <v>0.23633333333333334</v>
       </c>
       <c r="W69">
-        <v>0.9082083333333334</v>
+        <v>0.29633333333333334</v>
       </c>
       <c r="X69">
-        <v>0.87820833333333337</v>
+        <v>0.26633333333333331</v>
       </c>
       <c r="Y69">
-        <v>72.650000000000006</v>
+        <v>98.65</v>
       </c>
       <c r="Z69">
-        <v>77.650000000000006</v>
+        <v>98.9</v>
       </c>
       <c r="AA69">
-        <v>75.150000000000006</v>
+        <v>98.775000000000006</v>
       </c>
       <c r="AB69">
-        <v>1.3841041378138383</v>
+        <v>0.60292867936302397</v>
       </c>
       <c r="AC69">
-        <v>1.10458508165199</v>
+        <v>0.49038039538737976</v>
       </c>
       <c r="AD69">
-        <v>1.2419121695219573</v>
+        <v>0.54660318203247904</v>
       </c>
       <c r="AE69" t="s">
         <v>40</v>
       </c>
       <c r="AF69" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
@@ -8615,88 +8600,88 @@
         <v>437</v>
       </c>
       <c r="C70" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D70" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E70" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F70" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G70" t="s">
+        <v>433</v>
+      </c>
+      <c r="H70" t="s">
+        <v>434</v>
+      </c>
+      <c r="I70" t="s">
         <v>438</v>
       </c>
-      <c r="H70" t="s">
-        <v>439</v>
-      </c>
-      <c r="I70" t="s">
-        <v>440</v>
-      </c>
       <c r="J70">
-        <v>102.46666666666667</v>
+        <v>151.16666666666666</v>
       </c>
       <c r="K70">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L70">
         <v>150000000</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="N70">
-        <v>100.434</v>
+        <v>100.384</v>
       </c>
       <c r="O70">
-        <v>2.2833333333333332</v>
+        <v>6.2666666666666666</v>
       </c>
       <c r="P70">
-        <v>-5.1439549807383636E-4</v>
+        <v>1.6871933486249675E-3</v>
       </c>
       <c r="Q70">
-        <v>21.356045019261636</v>
+        <v>22.121933486249674</v>
       </c>
       <c r="R70">
-        <v>-2.65E-3</v>
+        <v>-5.2499999999999997E-4</v>
       </c>
       <c r="S70">
-        <v>35.621449650466865</v>
+        <v>31.693139052662357</v>
       </c>
       <c r="T70">
-        <v>28.927989148241785</v>
+        <v>25.005974984360247</v>
       </c>
       <c r="U70">
-        <v>32.272892840525692</v>
+        <v>28.345535052462566</v>
       </c>
       <c r="V70">
-        <v>0.14520833333333333</v>
+        <v>0.41949999999999998</v>
       </c>
       <c r="W70">
-        <v>0.20520833333333333</v>
+        <v>0.47949999999999998</v>
       </c>
       <c r="X70">
-        <v>0.17520833333333333</v>
+        <v>0.44950000000000001</v>
       </c>
       <c r="Y70">
-        <v>98.8</v>
+        <v>96.55</v>
       </c>
       <c r="Z70">
-        <v>98.95</v>
+        <v>96.95</v>
       </c>
       <c r="AA70">
-        <v>98.875</v>
+        <v>96.75</v>
       </c>
       <c r="AB70">
-        <v>0.53142282983800193</v>
+        <v>0.76643139052662357</v>
       </c>
       <c r="AC70">
-        <v>0.46448822481575114</v>
+        <v>0.69955974984360247</v>
       </c>
       <c r="AD70">
-        <v>0.49793726173859021</v>
+        <v>0.73295535052462568</v>
       </c>
       <c r="AE70" t="s">
         <v>40</v>
@@ -8707,198 +8692,198 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>439</v>
+      </c>
+      <c r="B71" t="s">
+        <v>440</v>
+      </c>
+      <c r="C71" t="s">
+        <v>419</v>
+      </c>
+      <c r="D71" t="s">
+        <v>420</v>
+      </c>
+      <c r="E71" t="s">
+        <v>421</v>
+      </c>
+      <c r="F71" t="s">
+        <v>422</v>
+      </c>
+      <c r="G71" t="s">
         <v>441</v>
       </c>
-      <c r="B71" t="s">
+      <c r="H71" t="s">
+        <v>262</v>
+      </c>
+      <c r="I71" t="s">
         <v>442</v>
       </c>
-      <c r="C71" t="s">
-        <v>424</v>
-      </c>
-      <c r="D71" t="s">
-        <v>425</v>
-      </c>
-      <c r="E71" t="s">
-        <v>426</v>
-      </c>
-      <c r="F71" t="s">
-        <v>427</v>
-      </c>
-      <c r="G71" t="s">
-        <v>438</v>
-      </c>
-      <c r="H71" t="s">
-        <v>439</v>
-      </c>
-      <c r="I71" t="s">
-        <v>443</v>
-      </c>
       <c r="J71">
-        <v>151.16666666666666</v>
+        <v>167.36666666666667</v>
       </c>
       <c r="K71">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L71">
-        <v>150000000</v>
+        <v>125000000</v>
       </c>
       <c r="M71">
-        <v>2E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="N71">
-        <v>100.384</v>
+        <v>100.264</v>
       </c>
       <c r="O71">
-        <v>6.2833333333333332</v>
+        <v>8.2666666666666675</v>
       </c>
       <c r="P71">
-        <v>1.6871933486249675E-3</v>
+        <v>1.3061319103151944E-3</v>
       </c>
       <c r="Q71">
-        <v>22.121933486249674</v>
+        <v>37.811319103151938</v>
       </c>
       <c r="R71">
-        <v>-5.2499999999999997E-4</v>
+        <v>-2.4749999999999998E-3</v>
       </c>
       <c r="S71">
-        <v>34.156163312589193</v>
+        <v>36.761917331052999</v>
       </c>
       <c r="T71">
-        <v>25.004953137113116</v>
+        <v>23.771796074644811</v>
       </c>
       <c r="U71">
-        <v>29.573006670067194</v>
+        <v>30.247522040122512</v>
       </c>
       <c r="V71">
-        <v>0.37666666666666665</v>
+        <v>0.50950000000000006</v>
       </c>
       <c r="W71">
-        <v>0.43666666666666665</v>
+        <v>0.56950000000000001</v>
       </c>
       <c r="X71">
-        <v>0.40666666666666662</v>
+        <v>0.53949999999999998</v>
       </c>
       <c r="Y71">
-        <v>96.65</v>
+        <v>94</v>
       </c>
       <c r="Z71">
-        <v>97.2</v>
+        <v>95</v>
       </c>
       <c r="AA71">
-        <v>96.925000000000011</v>
+        <v>94.5</v>
       </c>
       <c r="AB71">
-        <v>0.74822829979255856</v>
+        <v>0.90711917331052994</v>
       </c>
       <c r="AC71">
-        <v>0.65671619803779779</v>
+        <v>0.77721796074644811</v>
       </c>
       <c r="AD71">
-        <v>0.70239673336733854</v>
+        <v>0.84197522040122508</v>
       </c>
       <c r="AE71" t="s">
         <v>40</v>
       </c>
       <c r="AF71" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>443</v>
+      </c>
+      <c r="B72" t="s">
         <v>444</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>419</v>
+      </c>
+      <c r="D72" t="s">
+        <v>420</v>
+      </c>
+      <c r="E72" t="s">
+        <v>421</v>
+      </c>
+      <c r="F72" t="s">
+        <v>422</v>
+      </c>
+      <c r="G72" t="s">
         <v>445</v>
       </c>
-      <c r="C72" t="s">
-        <v>424</v>
-      </c>
-      <c r="D72" t="s">
-        <v>425</v>
-      </c>
-      <c r="E72" t="s">
-        <v>426</v>
-      </c>
-      <c r="F72" t="s">
-        <v>427</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>446</v>
-      </c>
-      <c r="H72" t="s">
-        <v>267</v>
       </c>
       <c r="I72" t="s">
         <v>447</v>
       </c>
       <c r="J72">
-        <v>167.36666666666667</v>
+        <v>189.7</v>
       </c>
       <c r="K72">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L72">
-        <v>125000000</v>
+        <v>130000000</v>
       </c>
       <c r="M72">
-        <v>1.5E-3</v>
+        <v>1.25E-3</v>
       </c>
       <c r="N72">
-        <v>100.264</v>
+        <v>100.078</v>
       </c>
       <c r="O72">
-        <v>8.2833333333333332</v>
+        <v>10.266666666666667</v>
       </c>
       <c r="P72">
-        <v>1.3061319103151944E-3</v>
-      </c>
-      <c r="Q72">
-        <v>37.811319103151938</v>
-      </c>
-      <c r="R72">
-        <v>-2.4749999999999998E-3</v>
+        <v>1.1994354744049951E-3</v>
+      </c>
+      <c r="Q72" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R72" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="S72">
-        <v>35.659014199884417</v>
+        <v>36.043543244809669</v>
       </c>
       <c r="T72">
-        <v>13.802074697982514</v>
+        <v>26.366631837179554</v>
       </c>
       <c r="U72">
-        <v>24.67565857110565</v>
+        <v>31.192055456166511</v>
       </c>
       <c r="V72">
-        <v>0.47345833333333331</v>
+        <v>0.59950000000000003</v>
       </c>
       <c r="W72">
-        <v>0.53345833333333337</v>
+        <v>0.65949999999999998</v>
       </c>
       <c r="X72">
-        <v>0.50345833333333334</v>
+        <v>0.62949999999999995</v>
       </c>
       <c r="Y72">
-        <v>94.35</v>
+        <v>91.6</v>
       </c>
       <c r="Z72">
-        <v>96.05</v>
+        <v>92.5</v>
       </c>
       <c r="AA72">
-        <v>95.199999999999989</v>
+        <v>92.05</v>
       </c>
       <c r="AB72">
-        <v>0.86004847533217754</v>
+        <v>0.98993543244809667</v>
       </c>
       <c r="AC72">
-        <v>0.64147908031315848</v>
+        <v>0.8931663183717955</v>
       </c>
       <c r="AD72">
-        <v>0.75021491904438986</v>
+        <v>0.94142055456166507</v>
       </c>
       <c r="AE72" t="s">
         <v>40</v>
       </c>
       <c r="AF72" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.25">
@@ -8909,16 +8894,16 @@
         <v>449</v>
       </c>
       <c r="C73" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D73" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E73" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G73" t="s">
         <v>450</v>
@@ -8930,367 +8915,367 @@
         <v>452</v>
       </c>
       <c r="J73">
-        <v>189.7</v>
+        <v>143.03333333333333</v>
       </c>
       <c r="K73">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L73">
-        <v>130000000</v>
+        <v>110000000</v>
       </c>
       <c r="M73">
-        <v>1.25E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N73">
-        <v>100.078</v>
+        <v>100.367</v>
       </c>
       <c r="O73">
-        <v>10.283333333333333</v>
+        <v>7.2666666666666666</v>
       </c>
       <c r="P73">
-        <v>1.1994354744049951E-3</v>
-      </c>
-      <c r="Q73" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R73" t="e">
-        <v>#VALUE!</v>
+        <v>1.872857835095899E-4</v>
+      </c>
+      <c r="Q73">
+        <v>16.8728578350959</v>
+      </c>
+      <c r="R73">
+        <v>-1.5E-3</v>
       </c>
       <c r="S73">
-        <v>36.313605355843116</v>
+        <v>32.455652080884015</v>
       </c>
       <c r="T73">
-        <v>26.681238973133738</v>
+        <v>22.937175517930168</v>
       </c>
       <c r="U73">
-        <v>31.484487085144597</v>
+        <v>27.68713461988483</v>
       </c>
       <c r="V73">
-        <v>0.5684583333333334</v>
+        <v>0.46450000000000002</v>
       </c>
       <c r="W73">
-        <v>0.62845833333333334</v>
+        <v>0.52449999999999997</v>
       </c>
       <c r="X73">
-        <v>0.59845833333333331</v>
+        <v>0.4945</v>
       </c>
       <c r="Y73">
-        <v>91.85</v>
+        <v>94.6</v>
       </c>
       <c r="Z73">
-        <v>92.75</v>
+        <v>95.25</v>
       </c>
       <c r="AA73">
-        <v>92.3</v>
+        <v>94.924999999999997</v>
       </c>
       <c r="AB73">
-        <v>0.96159438689176446</v>
+        <v>0.81905652080884017</v>
       </c>
       <c r="AC73">
-        <v>0.86527072306467068</v>
+        <v>0.72387175517930169</v>
       </c>
       <c r="AD73">
-        <v>0.91330320418477928</v>
+        <v>0.77137134619884828</v>
       </c>
       <c r="AE73" t="s">
         <v>40</v>
       </c>
       <c r="AF73" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C74" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D74" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E74" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G74" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="H74" t="s">
+        <v>451</v>
+      </c>
+      <c r="I74" t="s">
         <v>456</v>
       </c>
-      <c r="I74" t="s">
-        <v>457</v>
-      </c>
       <c r="J74">
-        <v>143.03333333333333</v>
+        <v>228.23333333333332</v>
       </c>
       <c r="K74">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L74">
-        <v>110000000</v>
+        <v>100000000</v>
       </c>
       <c r="M74">
-        <v>5.0000000000000001E-4</v>
+        <v>2E-3</v>
       </c>
       <c r="N74">
-        <v>100.367</v>
+        <v>100.809</v>
       </c>
       <c r="O74">
-        <v>7.2833333333333332</v>
+        <v>14.263888888888889</v>
       </c>
       <c r="P74">
-        <v>1.872857835095899E-4</v>
-      </c>
-      <c r="Q74">
-        <v>16.8728578350959</v>
-      </c>
-      <c r="R74">
-        <v>-1.5E-3</v>
+        <v>1.5617683942358812E-3</v>
+      </c>
+      <c r="Q74" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R74" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="S74">
-        <v>35.400191409824245</v>
+        <v>39.699389292921929</v>
       </c>
       <c r="T74">
-        <v>24.455732875080503</v>
+        <v>29.877131627409359</v>
       </c>
       <c r="U74">
-        <v>29.915667735038642</v>
+        <v>34.770150107802145</v>
       </c>
       <c r="V74">
-        <v>0.42595833333333333</v>
+        <v>0.74541666666666673</v>
       </c>
       <c r="W74">
-        <v>0.48595833333333333</v>
+        <v>0.80541666666666667</v>
       </c>
       <c r="X74">
-        <v>0.45595833333333335</v>
+        <v>0.77541666666666675</v>
       </c>
       <c r="Y74">
-        <v>94.65</v>
+        <v>87.3</v>
       </c>
       <c r="Z74">
-        <v>95.4</v>
+        <v>88.5</v>
       </c>
       <c r="AA74">
-        <v>95.025000000000006</v>
+        <v>87.9</v>
       </c>
       <c r="AB74">
-        <v>0.8099602474315758</v>
+        <v>1.172410559595886</v>
       </c>
       <c r="AC74">
-        <v>0.7005156620841384</v>
+        <v>1.0741879829407603</v>
       </c>
       <c r="AD74">
-        <v>0.75511501068371978</v>
+        <v>1.1231181677446882</v>
       </c>
       <c r="AE74" t="s">
         <v>40</v>
       </c>
       <c r="AF74" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>457</v>
+      </c>
+      <c r="B75" t="s">
+        <v>458</v>
+      </c>
+      <c r="C75" t="s">
+        <v>419</v>
+      </c>
+      <c r="D75" t="s">
+        <v>420</v>
+      </c>
+      <c r="E75" t="s">
+        <v>421</v>
+      </c>
+      <c r="F75" t="s">
+        <v>422</v>
+      </c>
+      <c r="G75" t="s">
         <v>459</v>
       </c>
-      <c r="B75" t="s">
+      <c r="H75" t="s">
+        <v>451</v>
+      </c>
+      <c r="I75" t="s">
         <v>460</v>
       </c>
-      <c r="C75" t="s">
-        <v>424</v>
-      </c>
-      <c r="D75" t="s">
-        <v>425</v>
-      </c>
-      <c r="E75" t="s">
-        <v>426</v>
-      </c>
-      <c r="F75" t="s">
-        <v>427</v>
-      </c>
-      <c r="G75" t="s">
-        <v>455</v>
-      </c>
-      <c r="H75" t="s">
-        <v>456</v>
-      </c>
-      <c r="I75" t="s">
-        <v>461</v>
-      </c>
       <c r="J75">
-        <v>228.23333333333332</v>
+        <v>57.8</v>
       </c>
       <c r="K75">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="M75">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>100.809</v>
+        <v>101.374</v>
       </c>
       <c r="O75">
-        <v>14.280555555555555</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="P75">
-        <v>1.5617683942358812E-3</v>
-      </c>
-      <c r="Q75" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R75" t="e">
-        <v>#VALUE!</v>
+        <v>-2.8688164462084306E-3</v>
+      </c>
+      <c r="Q75">
+        <v>24.311835537915695</v>
+      </c>
+      <c r="R75">
+        <v>-5.3E-3</v>
       </c>
       <c r="S75">
-        <v>39.301172278007023</v>
+        <v>26.317390301092765</v>
       </c>
       <c r="T75">
-        <v>29.925047843143226</v>
+        <v>7.1360456000436114</v>
       </c>
       <c r="U75">
-        <v>34.596586302535862</v>
+        <v>16.720925810430671</v>
       </c>
       <c r="V75">
-        <v>0.72771527777777778</v>
+        <v>-6.3053333333333322E-2</v>
       </c>
       <c r="W75">
-        <v>0.78771527777777783</v>
+        <v>-3.0533333333333315E-3</v>
       </c>
       <c r="X75">
-        <v>0.75771527777777781</v>
+        <v>-3.305333333333333E-2</v>
       </c>
       <c r="Y75">
-        <v>87.55</v>
+        <v>99.94</v>
       </c>
       <c r="Z75">
-        <v>88.7</v>
+        <v>99.99</v>
       </c>
       <c r="AA75">
-        <v>88.125</v>
+        <v>99.965000000000003</v>
       </c>
       <c r="AB75">
-        <v>1.150727000557848</v>
+        <v>0.23012056967759431</v>
       </c>
       <c r="AC75">
-        <v>1.0569657562092101</v>
+        <v>3.8307122667102789E-2</v>
       </c>
       <c r="AD75">
-        <v>1.1036811408031364</v>
+        <v>0.13415592477097338</v>
       </c>
       <c r="AE75" t="s">
         <v>40</v>
       </c>
       <c r="AF75" t="s">
-        <v>458</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>461</v>
+      </c>
+      <c r="B76" t="s">
         <v>462</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>419</v>
+      </c>
+      <c r="D76" t="s">
+        <v>420</v>
+      </c>
+      <c r="E76" t="s">
+        <v>421</v>
+      </c>
+      <c r="F76" t="s">
+        <v>422</v>
+      </c>
+      <c r="G76" t="s">
         <v>463</v>
       </c>
-      <c r="C76" t="s">
-        <v>424</v>
-      </c>
-      <c r="D76" t="s">
-        <v>425</v>
-      </c>
-      <c r="E76" t="s">
-        <v>426</v>
-      </c>
-      <c r="F76" t="s">
-        <v>427</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>464</v>
-      </c>
-      <c r="H76" t="s">
-        <v>456</v>
       </c>
       <c r="I76" t="s">
         <v>465</v>
       </c>
       <c r="J76">
-        <v>57.8</v>
+        <v>60.866666666666667</v>
       </c>
       <c r="K76">
         <v>5</v>
       </c>
       <c r="L76">
-        <v>150000000</v>
+        <v>175000000</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>1.1000000000000001E-2</v>
       </c>
       <c r="N76">
-        <v>101.374</v>
+        <v>100.218</v>
       </c>
       <c r="O76">
-        <v>0.28333333333333333</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="P76">
-        <v>-2.8688164462084306E-3</v>
+        <v>1.0550103914832541E-2</v>
       </c>
       <c r="Q76">
-        <v>24.311835537915695</v>
+        <v>32.751039148325411</v>
       </c>
       <c r="R76">
-        <v>-5.3E-3</v>
+        <v>7.2750000000000002E-3</v>
       </c>
       <c r="S76">
-        <v>18.078591231744635</v>
+        <v>37.774730613086724</v>
       </c>
       <c r="T76">
-        <v>7.2661614879551486</v>
+        <v>23.538682620621049</v>
       </c>
       <c r="U76">
-        <v>12.670510749332708</v>
+        <v>30.651010998750504</v>
       </c>
       <c r="V76">
-        <v>-6.6653333333333328E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="W76">
-        <v>-6.653333333333334E-3</v>
+        <v>0.19333333333333333</v>
       </c>
       <c r="X76">
-        <v>-3.6653333333333329E-2</v>
+        <v>0.16333333333333333</v>
       </c>
       <c r="Y76">
-        <v>99.96</v>
+        <v>100.7</v>
       </c>
       <c r="Z76">
-        <v>99.99</v>
+        <v>100.88</v>
       </c>
       <c r="AA76">
-        <v>99.974999999999994</v>
+        <v>100.78999999999999</v>
       </c>
       <c r="AB76">
-        <v>0.14413257898411302</v>
+        <v>0.5410806394642006</v>
       </c>
       <c r="AC76">
-        <v>3.6008281546218157E-2</v>
+        <v>0.39872015953954382</v>
       </c>
       <c r="AD76">
-        <v>9.0051774159993769E-2</v>
+        <v>0.46984344332083838</v>
       </c>
       <c r="AE76" t="s">
         <v>40</v>
       </c>
       <c r="AF76" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
@@ -9301,16 +9286,16 @@
         <v>467</v>
       </c>
       <c r="C77" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D77" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E77" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F77" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G77" t="s">
         <v>468</v>
@@ -9319,70 +9304,70 @@
         <v>469</v>
       </c>
       <c r="I77" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="J77">
-        <v>60.866666666666667</v>
+        <v>36.533333333333331</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>175000000</v>
+        <v>200000000</v>
       </c>
       <c r="M77">
-        <v>1.1000000000000001E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="N77">
-        <v>100.218</v>
+        <v>100.014</v>
       </c>
       <c r="O77">
-        <v>1.2833333333333334</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="P77">
-        <v>1.0550103914832541E-2</v>
+        <v>1.8951553452875757E-2</v>
       </c>
       <c r="Q77">
-        <v>32.751039148325411</v>
+        <v>8.015534528757577</v>
       </c>
       <c r="R77">
-        <v>7.2750000000000002E-3</v>
+        <v>1.8149999999999999E-2</v>
       </c>
       <c r="S77">
-        <v>33.993380865614562</v>
+        <v>28.191366707371429</v>
       </c>
       <c r="T77">
-        <v>22.31090107673122</v>
+        <v>13.124952004268076</v>
       </c>
       <c r="U77">
-        <v>28.148273528561752</v>
+        <v>20.654587200933292</v>
       </c>
       <c r="V77">
-        <v>6.1208333333333351E-2</v>
+        <v>-6.3053333333333322E-2</v>
       </c>
       <c r="W77">
-        <v>0.12120833333333335</v>
+        <v>-3.0533333333333315E-3</v>
       </c>
       <c r="X77">
-        <v>9.120833333333335E-2</v>
+        <v>-3.305333333333333E-2</v>
       </c>
       <c r="Y77">
-        <v>100.85</v>
+        <v>100.43</v>
       </c>
       <c r="Z77">
-        <v>101</v>
+        <v>100.47</v>
       </c>
       <c r="AA77">
-        <v>100.925</v>
+        <v>100.45</v>
       </c>
       <c r="AB77">
-        <v>0.43114214198947892</v>
+        <v>0.24886033374038097</v>
       </c>
       <c r="AC77">
-        <v>0.31431734410064555</v>
+        <v>9.8196186709347433E-2</v>
       </c>
       <c r="AD77">
-        <v>0.37269106861895085</v>
+        <v>0.17349253867599962</v>
       </c>
       <c r="AE77" t="s">
         <v>40</v>
@@ -9393,393 +9378,295 @@
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>470</v>
+      </c>
+      <c r="B78" t="s">
         <v>471</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>472</v>
       </c>
-      <c r="C78" t="s">
-        <v>424</v>
-      </c>
       <c r="D78" t="s">
-        <v>425</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>426</v>
+        <v>46</v>
       </c>
       <c r="F78" t="s">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="G78" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H78" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I78" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="J78">
-        <v>36.533333333333331</v>
+        <v>146.1</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L78">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="M78">
-        <v>1.9E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="N78">
-        <v>100.014</v>
+        <v>100.297</v>
       </c>
       <c r="O78">
-        <v>0.28333333333333333</v>
+        <v>7.5138888888888893</v>
       </c>
       <c r="P78">
-        <v>1.8951553452875757E-2</v>
+        <v>1.7496761871829134E-3</v>
       </c>
       <c r="Q78">
-        <v>8.015534528757577</v>
+        <v>23.746761871829133</v>
       </c>
       <c r="R78">
-        <v>1.8149999999999999E-2</v>
+        <v>-6.2500000000000001E-4</v>
       </c>
       <c r="S78">
-        <v>20.562845664817736</v>
+        <v>45.001614542040201</v>
       </c>
       <c r="T78">
-        <v>6.4136080848879198</v>
+        <v>33.603438626839797</v>
       </c>
       <c r="U78">
-        <v>13.485032358860066</v>
+        <v>39.288863213659873</v>
       </c>
       <c r="V78">
-        <v>-6.6653333333333328E-2</v>
+        <v>0.47562500000000002</v>
       </c>
       <c r="W78">
-        <v>-6.653333333333334E-3</v>
+        <v>0.53562500000000002</v>
       </c>
       <c r="X78">
-        <v>-3.6653333333333329E-2</v>
+        <v>0.50562499999999999</v>
       </c>
       <c r="Y78">
-        <v>100.48</v>
+        <v>94.55</v>
       </c>
       <c r="Z78">
-        <v>100.52</v>
+        <v>95.35</v>
       </c>
       <c r="AA78">
-        <v>100.5</v>
+        <v>94.949999999999989</v>
       </c>
       <c r="AB78">
-        <v>0.16897512331484402</v>
+        <v>0.95564114542040202</v>
       </c>
       <c r="AC78">
-        <v>2.7482747515545879E-2</v>
+        <v>0.84165938626839798</v>
       </c>
       <c r="AD78">
-        <v>9.8196990255267333E-2</v>
+        <v>0.89851363213659874</v>
       </c>
       <c r="AE78" t="s">
         <v>40</v>
       </c>
       <c r="AF78" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C79" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
-        <v>46</v>
+        <v>412</v>
       </c>
       <c r="F79" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G79" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H79" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I79" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J79">
-        <v>146.1</v>
+        <v>97.4</v>
       </c>
       <c r="K79">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L79">
         <v>100000000</v>
       </c>
       <c r="M79">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="N79">
-        <v>100.297</v>
+        <v>100.29900000000001</v>
       </c>
       <c r="O79">
-        <v>7.5305555555555559</v>
+        <v>3.5111111111111111</v>
       </c>
       <c r="P79">
-        <v>1.7496761871829134E-3</v>
+        <v>6.2519772882942647E-4</v>
       </c>
       <c r="Q79">
-        <v>23.746761871829133</v>
+        <v>30.001977288294267</v>
       </c>
       <c r="R79">
-        <v>-6.2500000000000001E-4</v>
+        <v>-2.3749999999999999E-3</v>
       </c>
       <c r="S79">
-        <v>39.378463739745008</v>
+        <v>44.695325860027204</v>
       </c>
       <c r="T79">
-        <v>30.201227329662416</v>
+        <v>32.943050340810018</v>
       </c>
       <c r="U79">
-        <v>34.780963354339022</v>
+        <v>38.81146770624985</v>
       </c>
       <c r="V79">
-        <v>0.43770138888888888</v>
+        <v>0.29049999999999998</v>
       </c>
       <c r="W79">
-        <v>0.49770138888888893</v>
+        <v>0.35049999999999998</v>
       </c>
       <c r="X79">
-        <v>0.4677013888888889</v>
+        <v>0.32050000000000001</v>
       </c>
       <c r="Y79">
-        <v>95.2</v>
+        <v>97.7</v>
       </c>
       <c r="Z79">
-        <v>95.85</v>
+        <v>98.1</v>
       </c>
       <c r="AA79">
-        <v>95.525000000000006</v>
+        <v>97.9</v>
       </c>
       <c r="AB79">
-        <v>0.86148602628633897</v>
+        <v>0.76745325860027203</v>
       </c>
       <c r="AC79">
-        <v>0.76971366218551307</v>
+        <v>0.64993050340810021</v>
       </c>
       <c r="AD79">
-        <v>0.81551102243227913</v>
+        <v>0.70861467706249848</v>
       </c>
       <c r="AE79" t="s">
         <v>40</v>
       </c>
       <c r="AF79" t="s">
-        <v>41</v>
+        <v>484</v>
       </c>
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C80" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="D80" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E80" t="s">
-        <v>417</v>
+        <v>46</v>
       </c>
       <c r="F80" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G80" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H80" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I80" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J80">
-        <v>97.4</v>
+        <v>170.43333333333334</v>
       </c>
       <c r="K80">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L80">
         <v>100000000</v>
       </c>
       <c r="M80">
-        <v>1E-3</v>
+        <v>1.8500000000000003E-2</v>
       </c>
       <c r="N80">
-        <v>100.29900000000001</v>
+        <v>100.55200000000001</v>
       </c>
       <c r="O80">
-        <v>3.5277777777777777</v>
+        <v>12.269444444444444</v>
       </c>
       <c r="P80">
-        <v>6.2519772882942647E-4</v>
+        <v>1.8050270319273511E-2</v>
       </c>
       <c r="Q80">
-        <v>30.001977288294267</v>
+        <v>45.50270319273509</v>
       </c>
       <c r="R80">
-        <v>-2.3749999999999999E-3</v>
+        <v>1.3500000000000002E-2</v>
       </c>
       <c r="S80">
-        <v>40.892682987014901</v>
+        <v>37.626310781625349</v>
       </c>
       <c r="T80">
-        <v>33.608722778314842</v>
+        <v>29.738594391627913</v>
       </c>
       <c r="U80">
-        <v>37.247723731585694</v>
+        <v>33.67258101416779</v>
       </c>
       <c r="V80">
-        <v>0.22298611111111111</v>
+        <v>0.68193055555555548</v>
       </c>
       <c r="W80">
-        <v>0.2829861111111111</v>
+        <v>0.74193055555555554</v>
       </c>
       <c r="X80">
-        <v>0.25298611111111108</v>
+        <v>0.71193055555555551</v>
       </c>
       <c r="Y80">
-        <v>98.05</v>
+        <v>108.7</v>
       </c>
       <c r="Z80">
-        <v>98.3</v>
+        <v>109.65</v>
       </c>
       <c r="AA80">
-        <v>98.174999999999997</v>
+        <v>109.17500000000001</v>
       </c>
       <c r="AB80">
-        <v>0.66191294098126008</v>
+        <v>1.088193663371809</v>
       </c>
       <c r="AC80">
-        <v>0.5890733388942595</v>
+        <v>1.0093164994718347</v>
       </c>
       <c r="AD80">
-        <v>0.62546334842696805</v>
+        <v>1.0486563656972334</v>
       </c>
       <c r="AE80" t="s">
         <v>40</v>
       </c>
       <c r="AF80" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>490</v>
-      </c>
-      <c r="B81" t="s">
-        <v>491</v>
-      </c>
-      <c r="C81" t="s">
-        <v>477</v>
-      </c>
-      <c r="D81" t="s">
-        <v>45</v>
-      </c>
-      <c r="E81" t="s">
-        <v>46</v>
-      </c>
-      <c r="F81" t="s">
-        <v>478</v>
-      </c>
-      <c r="G81" t="s">
-        <v>492</v>
-      </c>
-      <c r="H81" t="s">
-        <v>493</v>
-      </c>
-      <c r="I81" t="s">
-        <v>494</v>
-      </c>
-      <c r="J81">
-        <v>170.43333333333334</v>
-      </c>
-      <c r="K81">
-        <v>14</v>
-      </c>
-      <c r="L81">
-        <v>100000000</v>
-      </c>
-      <c r="M81">
-        <v>1.8500000000000003E-2</v>
-      </c>
-      <c r="N81">
-        <v>100.55200000000001</v>
-      </c>
-      <c r="O81">
-        <v>12.286111111111111</v>
-      </c>
-      <c r="P81">
-        <v>1.8050270319273511E-2</v>
-      </c>
-      <c r="Q81">
-        <v>45.50270319273509</v>
-      </c>
-      <c r="R81">
-        <v>1.3500000000000002E-2</v>
-      </c>
-      <c r="S81">
-        <v>39.183440791986001</v>
-      </c>
-      <c r="T81">
-        <v>30.07816715681798</v>
-      </c>
-      <c r="U81">
-        <v>34.617631692232187</v>
-      </c>
-      <c r="V81">
-        <v>0.65894444444444444</v>
-      </c>
-      <c r="W81">
-        <v>0.7189444444444445</v>
-      </c>
-      <c r="X81">
-        <v>0.68894444444444447</v>
-      </c>
-      <c r="Y81">
-        <v>108.8</v>
-      </c>
-      <c r="Z81">
-        <v>109.9</v>
-      </c>
-      <c r="AA81">
-        <v>109.35</v>
-      </c>
-      <c r="AB81">
-        <v>1.0807788523643045</v>
-      </c>
-      <c r="AC81">
-        <v>0.98972611601262428</v>
-      </c>
-      <c r="AD81">
-        <v>1.0351207613667663</v>
-      </c>
-      <c r="AE81" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF81" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Market data utilities.xlsx
+++ b/Market data utilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Macro\Python\Streamlit présentation Satom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C786263-45FE-4B2F-9BE6-AB4C503C81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B4E29F-D1DD-49A7-8056-6B247DA77696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
